--- a/Exp3_PTO_GRPO/eda/results/arms/questionnaires/tables/gpt-4o-mini/questionnaires.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/questionnaires/tables/gpt-4o-mini/questionnaires.xlsx
@@ -634,13 +634,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7" t="n">
         <v>2.938</v>
       </c>
       <c r="H7" t="n">
-        <v>0.948</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="8">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
         <v>2.927</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>1.135</v>
       </c>
     </row>
     <row r="9">
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
         <v>2.979</v>
       </c>
       <c r="H9" t="n">
-        <v>1.104</v>
+        <v>1.292</v>
       </c>
     </row>
     <row r="10">
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
         <v>2.667</v>
       </c>
       <c r="H10" t="n">
-        <v>1.177</v>
+        <v>1.531</v>
       </c>
     </row>
     <row r="11">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
         <v>3.042</v>
       </c>
       <c r="H11" t="n">
-        <v>1.156</v>
+        <v>1.365</v>
       </c>
     </row>
     <row r="12">
@@ -1214,13 +1214,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
         <v>2.938</v>
       </c>
       <c r="H27" t="n">
-        <v>1.01</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="28">
@@ -1243,13 +1243,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
         <v>2.927</v>
       </c>
       <c r="H28" t="n">
-        <v>1.062</v>
+        <v>1.135</v>
       </c>
     </row>
     <row r="29">
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
         <v>2.979</v>
       </c>
       <c r="H29" t="n">
-        <v>1.167</v>
+        <v>1.292</v>
       </c>
     </row>
     <row r="30">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G30" t="n">
         <v>2.667</v>
       </c>
       <c r="H30" t="n">
-        <v>1.354</v>
+        <v>1.531</v>
       </c>
     </row>
     <row r="31">
@@ -1330,13 +1330,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
         <v>3.042</v>
       </c>
       <c r="H31" t="n">
-        <v>1.354</v>
+        <v>1.365</v>
       </c>
     </row>
     <row r="32">
@@ -1924,13 +1924,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
         <v>3.323</v>
       </c>
       <c r="H9" t="n">
-        <v>0.354</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1955,13 +1955,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
         <v>2.729</v>
       </c>
       <c r="H10" t="n">
-        <v>0.365</v>
+        <v>0.479</v>
       </c>
     </row>
     <row r="11">
@@ -1986,13 +1986,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
         <v>3.062</v>
       </c>
       <c r="H11" t="n">
-        <v>0.625</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
         <v>0.471</v>
       </c>
       <c r="H12" t="n">
-        <v>0.107</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="13">
@@ -2048,13 +2048,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
         <v>0.395</v>
       </c>
       <c r="H13" t="n">
-        <v>0.113</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="14">
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
         <v>0.446</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.074</v>
+        <v>-0.121</v>
       </c>
     </row>
     <row r="15">
@@ -2110,13 +2110,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
         <v>0.159</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.039</v>
+        <v>-0.031</v>
       </c>
     </row>
     <row r="16">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G37" t="n">
         <v>3.323</v>
       </c>
       <c r="H37" t="n">
-        <v>0.479</v>
+        <v>0.5620000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -2823,13 +2823,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
         <v>2.729</v>
       </c>
       <c r="H38" t="n">
-        <v>0.417</v>
+        <v>0.479</v>
       </c>
     </row>
     <row r="39">
@@ -2854,13 +2854,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G39" t="n">
         <v>3.062</v>
       </c>
       <c r="H39" t="n">
-        <v>0.75</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G40" t="n">
         <v>0.471</v>
       </c>
       <c r="H40" t="n">
-        <v>0.143</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="41">
@@ -2916,13 +2916,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G41" t="n">
         <v>0.395</v>
       </c>
       <c r="H41" t="n">
-        <v>0.139</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="42">
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G42" t="n">
         <v>0.446</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.107</v>
+        <v>-0.121</v>
       </c>
     </row>
     <row r="43">
@@ -2978,13 +2978,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G43" t="n">
         <v>0.159</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.032</v>
+        <v>-0.031</v>
       </c>
     </row>
     <row r="44">
@@ -3432,7 +3432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4214,43 +4214,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>3.458</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.213</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.006</v>
-      </c>
       <c r="J19" t="n">
-        <v>0.059</v>
+        <v>0.046</v>
       </c>
       <c r="K19" t="n">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="L19" t="n">
-        <v>0.013</v>
+        <v>0.046</v>
       </c>
     </row>
     <row r="20">
@@ -4268,31 +4268,31 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>3.458</v>
       </c>
       <c r="F20" t="n">
-        <v>0.209</v>
+        <v>0.213</v>
       </c>
       <c r="G20" t="n">
-        <v>0.004</v>
+        <v>0.007</v>
       </c>
       <c r="H20" t="n">
-        <v>0.126</v>
+        <v>0.121</v>
       </c>
       <c r="I20" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="J20" t="n">
-        <v>0.041</v>
+        <v>0.059</v>
       </c>
       <c r="K20" t="n">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="L20" t="n">
-        <v>0.029</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="21">
@@ -4310,31 +4310,31 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>0.22</v>
+        <v>0.209</v>
       </c>
       <c r="G21" t="n">
         <v>0.004</v>
       </c>
       <c r="H21" t="n">
-        <v>0.159</v>
+        <v>0.126</v>
       </c>
       <c r="I21" t="n">
-        <v>0.002</v>
+        <v>0.005</v>
       </c>
       <c r="J21" t="n">
-        <v>0.033</v>
+        <v>0.041</v>
       </c>
       <c r="K21" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="L21" t="n">
-        <v>0.017</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="22">
@@ -4352,31 +4352,31 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
         <v>3</v>
       </c>
-      <c r="E22" t="n">
-        <v>2.667</v>
-      </c>
       <c r="F22" t="n">
-        <v>0.252</v>
+        <v>0.22</v>
       </c>
       <c r="G22" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="H22" t="n">
-        <v>0.174</v>
+        <v>0.159</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="J22" t="n">
-        <v>0.051</v>
+        <v>0.033</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="L22" t="n">
-        <v>0.026</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="23">
@@ -4394,31 +4394,31 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>2.406</v>
+        <v>2.667</v>
       </c>
       <c r="F23" t="n">
-        <v>0.215</v>
+        <v>0.252</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>0.142</v>
+        <v>0.174</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.038</v>
+        <v>0.051</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.034</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="24">
@@ -4436,31 +4436,31 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>2.594</v>
+        <v>2.406</v>
       </c>
       <c r="F24" t="n">
-        <v>0.289</v>
+        <v>0.215</v>
       </c>
       <c r="G24" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.188</v>
+        <v>0.142</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.057</v>
+        <v>0.038</v>
       </c>
       <c r="K24" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.037</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="25">
@@ -4478,31 +4478,31 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>2.531</v>
+        <v>2.594</v>
       </c>
       <c r="F25" t="n">
-        <v>0.318</v>
+        <v>0.289</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="H25" t="n">
-        <v>0.189</v>
+        <v>0.188</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.051</v>
+        <v>0.057</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="L25" t="n">
-        <v>0.077</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="26">
@@ -4520,31 +4520,31 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>2.479</v>
+        <v>2.531</v>
       </c>
       <c r="F26" t="n">
-        <v>0.341</v>
+        <v>0.318</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.167</v>
+        <v>0.189</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0.045</v>
+        <v>0.051</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.129</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="27">
@@ -4562,31 +4562,31 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>2.385</v>
+        <v>2.479</v>
       </c>
       <c r="F27" t="n">
-        <v>0.349</v>
+        <v>0.341</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.161</v>
+        <v>0.167</v>
       </c>
       <c r="I27" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.031</v>
+        <v>0.045</v>
       </c>
       <c r="K27" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.154</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="28">
@@ -4604,31 +4604,31 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.625</v>
+        <v>2.385</v>
       </c>
       <c r="F28" t="n">
-        <v>0.471</v>
+        <v>0.349</v>
       </c>
       <c r="G28" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.165</v>
+        <v>0.161</v>
       </c>
       <c r="I28" t="n">
         <v>0.001</v>
       </c>
       <c r="J28" t="n">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="L28" t="n">
-        <v>0.27</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="29">
@@ -4646,37 +4646,37 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>2.635</v>
+        <v>2.625</v>
       </c>
       <c r="F29" t="n">
-        <v>0.491</v>
+        <v>0.471</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>0.163</v>
+        <v>0.165</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03</v>
+        <v>0.033</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="L29" t="n">
-        <v>0.299</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4685,34 +4685,34 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.004</v>
-      </c>
       <c r="H30" t="n">
-        <v>0.109</v>
+        <v>0.163</v>
       </c>
       <c r="I30" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.044</v>
+        <v>0.03</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.008</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="31">
@@ -4730,31 +4730,31 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="F31" t="n">
-        <v>0.222</v>
+        <v>0.178</v>
       </c>
       <c r="G31" t="n">
         <v>0.004</v>
       </c>
       <c r="H31" t="n">
-        <v>0.139</v>
+        <v>0.109</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="J31" t="n">
-        <v>0.047</v>
+        <v>0.044</v>
       </c>
       <c r="K31" t="n">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
       <c r="L31" t="n">
-        <v>0.031</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="32">
@@ -4772,31 +4772,31 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.188</v>
+        <v>3.25</v>
       </c>
       <c r="F32" t="n">
-        <v>0.231</v>
+        <v>0.222</v>
       </c>
       <c r="G32" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="H32" t="n">
-        <v>0.141</v>
+        <v>0.139</v>
       </c>
       <c r="I32" t="n">
-        <v>0.003</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.058</v>
+        <v>0.047</v>
       </c>
       <c r="K32" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="L32" t="n">
-        <v>0.017</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="33">
@@ -4814,31 +4814,31 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.938</v>
+        <v>3.188</v>
       </c>
       <c r="F33" t="n">
-        <v>0.248</v>
+        <v>0.231</v>
       </c>
       <c r="G33" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="H33" t="n">
-        <v>0.17</v>
+        <v>0.141</v>
       </c>
       <c r="I33" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="J33" t="n">
-        <v>0.046</v>
+        <v>0.058</v>
       </c>
       <c r="K33" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="L33" t="n">
-        <v>0.028</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="34">
@@ -4856,31 +4856,31 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.854</v>
+        <v>2.938</v>
       </c>
       <c r="F34" t="n">
-        <v>0.326</v>
+        <v>0.248</v>
       </c>
       <c r="G34" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="I34" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="K34" t="n">
         <v>0.002</v>
       </c>
-      <c r="J34" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.003</v>
-      </c>
       <c r="L34" t="n">
-        <v>0.043</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="35">
@@ -4898,31 +4898,31 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>2.875</v>
+        <v>2.854</v>
       </c>
       <c r="F35" t="n">
-        <v>0.325</v>
+        <v>0.326</v>
       </c>
       <c r="G35" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
       <c r="H35" t="n">
-        <v>0.224</v>
+        <v>0.21</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="J35" t="n">
-        <v>0.062</v>
+        <v>0.063</v>
       </c>
       <c r="K35" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="L35" t="n">
-        <v>0.034</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="36">
@@ -4940,31 +4940,31 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>3.01</v>
+        <v>2.875</v>
       </c>
       <c r="F36" t="n">
-        <v>0.32</v>
+        <v>0.325</v>
       </c>
       <c r="G36" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H36" t="n">
-        <v>0.207</v>
+        <v>0.224</v>
       </c>
       <c r="I36" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="K36" t="n">
         <v>0.002</v>
       </c>
       <c r="L36" t="n">
-        <v>0.036</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="37">
@@ -4982,31 +4982,31 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>2.719</v>
+        <v>3.01</v>
       </c>
       <c r="F37" t="n">
-        <v>0.263</v>
+        <v>0.32</v>
       </c>
       <c r="G37" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="H37" t="n">
-        <v>0.18</v>
+        <v>0.207</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="J37" t="n">
-        <v>0.041</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="L37" t="n">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="38">
@@ -5024,31 +5024,31 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>2.865</v>
+        <v>2.719</v>
       </c>
       <c r="F38" t="n">
-        <v>0.29</v>
+        <v>0.263</v>
       </c>
       <c r="G38" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="H38" t="n">
-        <v>0.181</v>
+        <v>0.18</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.062</v>
+        <v>0.041</v>
       </c>
       <c r="K38" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
       <c r="L38" t="n">
-        <v>0.042</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="39">
@@ -5066,31 +5066,31 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>2.812</v>
+        <v>2.865</v>
       </c>
       <c r="F39" t="n">
-        <v>0.269</v>
+        <v>0.29</v>
       </c>
       <c r="G39" t="n">
         <v>0.003</v>
       </c>
       <c r="H39" t="n">
-        <v>0.168</v>
+        <v>0.181</v>
       </c>
       <c r="I39" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0.054</v>
+        <v>0.062</v>
       </c>
       <c r="K39" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="L39" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="40">
@@ -5108,30 +5108,72 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E40" t="n">
-        <v>2.823</v>
+        <v>2.812</v>
       </c>
       <c r="F40" t="n">
-        <v>0.264</v>
+        <v>0.269</v>
       </c>
       <c r="G40" t="n">
-        <v>0.006</v>
+        <v>0.003</v>
       </c>
       <c r="H40" t="n">
-        <v>0.154</v>
+        <v>0.168</v>
       </c>
       <c r="I40" t="n">
         <v>0.001</v>
       </c>
       <c r="J40" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.041</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.823</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J41" t="n">
         <v>0.056</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K41" t="n">
         <v>0.004</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L41" t="n">
         <v>0.043</v>
       </c>
     </row>
@@ -5470,13 +5512,13 @@
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
         <v>3.427</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.51</v>
+        <v>-0.6879999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -5502,13 +5544,13 @@
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
         <v>0.209</v>
       </c>
       <c r="H11" t="n">
-        <v>0.131</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -5534,13 +5576,13 @@
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
         <v>0.006</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.004</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="13">
@@ -5566,13 +5608,13 @@
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
         <v>0.121</v>
       </c>
       <c r="H13" t="n">
-        <v>0.117</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="14">
@@ -5598,13 +5640,13 @@
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
         <v>0.002</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="15">
@@ -5630,13 +5672,13 @@
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
         <v>0.045</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="16">
@@ -5662,13 +5704,13 @@
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
         <v>0.01</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.008</v>
+        <v>-0.007</v>
       </c>
     </row>
     <row r="17">
@@ -5694,13 +5736,13 @@
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
         <v>0.026</v>
       </c>
       <c r="H17" t="n">
-        <v>0.006</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="18">
@@ -6494,13 +6536,13 @@
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G42" t="n">
         <v>3.427</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.667</v>
+        <v>-0.6879999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -6526,13 +6568,13 @@
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G43" t="n">
         <v>0.209</v>
       </c>
       <c r="H43" t="n">
-        <v>0.096</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -6558,13 +6600,13 @@
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G44" t="n">
         <v>0.006</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.005</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="45">
@@ -6590,13 +6632,13 @@
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G45" t="n">
         <v>0.121</v>
       </c>
       <c r="H45" t="n">
-        <v>0.082</v>
+        <v>0.062</v>
       </c>
     </row>
     <row r="46">
@@ -6622,7 +6664,7 @@
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G46" t="n">
         <v>0.002</v>
@@ -6654,13 +6696,13 @@
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G47" t="n">
         <v>0.045</v>
       </c>
       <c r="H47" t="n">
-        <v>0.012</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="48">
@@ -6686,13 +6728,13 @@
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G48" t="n">
         <v>0.01</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.008</v>
+        <v>-0.007</v>
       </c>
     </row>
     <row r="49">
@@ -6718,13 +6760,13 @@
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G49" t="n">
         <v>0.026</v>
       </c>
       <c r="H49" t="n">
-        <v>0.017</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="50">
@@ -7898,13 +7940,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
         <v>3.042</v>
       </c>
       <c r="H19" t="n">
-        <v>0.729</v>
+        <v>0.781</v>
       </c>
     </row>
     <row r="20">
@@ -7932,13 +7974,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
         <v>2.604</v>
       </c>
       <c r="H20" t="n">
-        <v>1.104</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="21">
@@ -7966,13 +8008,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
         <v>2.167</v>
       </c>
       <c r="H21" t="n">
-        <v>0.729</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="22">
@@ -8000,13 +8042,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
         <v>3.156</v>
       </c>
       <c r="H22" t="n">
-        <v>1.052</v>
+        <v>1.177</v>
       </c>
     </row>
     <row r="23">
@@ -8034,13 +8076,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
         <v>3.177</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>1.104</v>
       </c>
     </row>
     <row r="24">
@@ -8068,13 +8110,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
         <v>2.688</v>
       </c>
       <c r="H24" t="n">
-        <v>1.104</v>
+        <v>1.438</v>
       </c>
     </row>
     <row r="25">
@@ -8102,13 +8144,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>3.417</v>
       </c>
       <c r="H25" t="n">
-        <v>1.083</v>
+        <v>1.146</v>
       </c>
     </row>
     <row r="26">
@@ -8136,13 +8178,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
         <v>3.406</v>
       </c>
       <c r="H26" t="n">
-        <v>1.125</v>
+        <v>1.219</v>
       </c>
     </row>
     <row r="27">
@@ -8170,13 +8212,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
         <v>2.677</v>
       </c>
       <c r="H27" t="n">
-        <v>1.125</v>
+        <v>1.365</v>
       </c>
     </row>
     <row r="28">
@@ -8204,13 +8246,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
         <v>2.302</v>
       </c>
       <c r="H28" t="n">
-        <v>0.948</v>
+        <v>1.042</v>
       </c>
     </row>
     <row r="29">
@@ -8238,13 +8280,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
         <v>3.417</v>
       </c>
       <c r="H29" t="n">
-        <v>1.115</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="30">
@@ -8272,13 +8314,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G30" t="n">
         <v>3.406</v>
       </c>
       <c r="H30" t="n">
-        <v>1.125</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="31">
@@ -8306,13 +8348,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
         <v>2.979</v>
       </c>
       <c r="H31" t="n">
-        <v>0.979</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="32">
@@ -8340,13 +8382,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
         <v>3.385</v>
       </c>
       <c r="H32" t="n">
-        <v>1.26</v>
+        <v>1.396</v>
       </c>
     </row>
     <row r="33">
@@ -8374,13 +8416,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
         <v>3.26</v>
       </c>
       <c r="H33" t="n">
-        <v>1.281</v>
+        <v>1.448</v>
       </c>
     </row>
     <row r="34">
@@ -8408,13 +8450,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G34" t="n">
         <v>3.135</v>
       </c>
       <c r="H34" t="n">
-        <v>1.281</v>
+        <v>1.469</v>
       </c>
     </row>
     <row r="35">
@@ -8442,13 +8484,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G35" t="n">
         <v>3.052</v>
       </c>
       <c r="H35" t="n">
-        <v>1.312</v>
+        <v>1.542</v>
       </c>
     </row>
     <row r="36">
@@ -10210,13 +10252,13 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G87" t="n">
         <v>3.042</v>
       </c>
       <c r="H87" t="n">
-        <v>0.76</v>
+        <v>0.781</v>
       </c>
     </row>
     <row r="88">
@@ -10244,13 +10286,13 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G88" t="n">
         <v>2.604</v>
       </c>
       <c r="H88" t="n">
-        <v>1.031</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="89">
@@ -10278,13 +10320,13 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G89" t="n">
         <v>2.167</v>
       </c>
       <c r="H89" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="90">
@@ -10312,13 +10354,13 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G90" t="n">
         <v>3.156</v>
       </c>
       <c r="H90" t="n">
-        <v>1.01</v>
+        <v>1.177</v>
       </c>
     </row>
     <row r="91">
@@ -10346,13 +10388,13 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G91" t="n">
         <v>3.177</v>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>1.104</v>
       </c>
     </row>
     <row r="92">
@@ -10380,13 +10422,13 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G92" t="n">
         <v>2.688</v>
       </c>
       <c r="H92" t="n">
-        <v>1.156</v>
+        <v>1.438</v>
       </c>
     </row>
     <row r="93">
@@ -10414,13 +10456,13 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G93" t="n">
         <v>3.417</v>
       </c>
       <c r="H93" t="n">
-        <v>1.135</v>
+        <v>1.146</v>
       </c>
     </row>
     <row r="94">
@@ -10448,13 +10490,13 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G94" t="n">
         <v>3.406</v>
       </c>
       <c r="H94" t="n">
-        <v>1.177</v>
+        <v>1.219</v>
       </c>
     </row>
     <row r="95">
@@ -10482,13 +10524,13 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G95" t="n">
         <v>2.677</v>
       </c>
       <c r="H95" t="n">
-        <v>1.135</v>
+        <v>1.365</v>
       </c>
     </row>
     <row r="96">
@@ -10516,13 +10558,13 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G96" t="n">
         <v>2.302</v>
       </c>
       <c r="H96" t="n">
-        <v>0.844</v>
+        <v>1.042</v>
       </c>
     </row>
     <row r="97">
@@ -10550,13 +10592,13 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G97" t="n">
         <v>3.417</v>
       </c>
       <c r="H97" t="n">
-        <v>1.198</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="98">
@@ -10584,13 +10626,13 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G98" t="n">
         <v>3.406</v>
       </c>
       <c r="H98" t="n">
-        <v>1.208</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="99">
@@ -10618,13 +10660,13 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G99" t="n">
         <v>2.979</v>
       </c>
       <c r="H99" t="n">
-        <v>1.083</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="100">
@@ -10652,13 +10694,13 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G100" t="n">
         <v>3.385</v>
       </c>
       <c r="H100" t="n">
-        <v>1.406</v>
+        <v>1.396</v>
       </c>
     </row>
     <row r="101">
@@ -10686,13 +10728,13 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G101" t="n">
         <v>3.26</v>
       </c>
       <c r="H101" t="n">
-        <v>1.438</v>
+        <v>1.448</v>
       </c>
     </row>
     <row r="102">
@@ -10720,13 +10762,13 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G102" t="n">
         <v>3.135</v>
       </c>
       <c r="H102" t="n">
-        <v>1.427</v>
+        <v>1.469</v>
       </c>
     </row>
     <row r="103">
@@ -10754,13 +10796,13 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G103" t="n">
         <v>3.052</v>
       </c>
       <c r="H103" t="n">
-        <v>1.406</v>
+        <v>1.542</v>
       </c>
     </row>
     <row r="104">
@@ -12343,13 +12385,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
         <v>2.604</v>
       </c>
       <c r="H14" t="n">
-        <v>0.469</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="15">
@@ -12372,13 +12414,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
         <v>2.76</v>
       </c>
       <c r="H15" t="n">
-        <v>0.615</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="16">
@@ -12401,13 +12443,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
         <v>3.115</v>
       </c>
       <c r="H16" t="n">
-        <v>0.417</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="17">
@@ -12430,13 +12472,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
         <v>2.531</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="18">
@@ -12459,13 +12501,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
         <v>3.354</v>
       </c>
       <c r="H18" t="n">
-        <v>0.542</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="19">
@@ -12488,13 +12530,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
         <v>2.521</v>
       </c>
       <c r="H19" t="n">
-        <v>0.552</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="20">
@@ -12517,13 +12559,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
         <v>3.01</v>
       </c>
       <c r="H20" t="n">
-        <v>0.531</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="21">
@@ -12546,13 +12588,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
         <v>2.75</v>
       </c>
       <c r="H21" t="n">
-        <v>0.771</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="22">
@@ -12575,13 +12617,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
         <v>3.354</v>
       </c>
       <c r="H22" t="n">
-        <v>0.604</v>
+        <v>0.646</v>
       </c>
     </row>
     <row r="23">
@@ -12604,13 +12646,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
         <v>2.865</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="24">
@@ -12633,13 +12675,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
         <v>2.719</v>
       </c>
       <c r="H24" t="n">
-        <v>0.719</v>
+        <v>0.896</v>
       </c>
     </row>
     <row r="25">
@@ -12662,13 +12704,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>2.698</v>
       </c>
       <c r="H25" t="n">
-        <v>0.75</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="26">
@@ -13735,13 +13777,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G62" t="n">
         <v>2.604</v>
       </c>
       <c r="H62" t="n">
-        <v>0.469</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="63">
@@ -13764,13 +13806,13 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G63" t="n">
         <v>2.76</v>
       </c>
       <c r="H63" t="n">
-        <v>0.615</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="64">
@@ -13793,13 +13835,13 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G64" t="n">
         <v>3.115</v>
       </c>
       <c r="H64" t="n">
-        <v>0.417</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="65">
@@ -13822,13 +13864,13 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G65" t="n">
         <v>2.531</v>
       </c>
       <c r="H65" t="n">
-        <v>0.448</v>
+        <v>0.469</v>
       </c>
     </row>
     <row r="66">
@@ -13851,13 +13893,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G66" t="n">
         <v>3.354</v>
       </c>
       <c r="H66" t="n">
-        <v>0.469</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="67">
@@ -13880,13 +13922,13 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G67" t="n">
         <v>2.521</v>
       </c>
       <c r="H67" t="n">
-        <v>0.469</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="68">
@@ -13909,13 +13951,13 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G68" t="n">
         <v>3.01</v>
       </c>
       <c r="H68" t="n">
-        <v>0.583</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="69">
@@ -13938,13 +13980,13 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G69" t="n">
         <v>2.75</v>
       </c>
       <c r="H69" t="n">
-        <v>0.708</v>
+        <v>0.854</v>
       </c>
     </row>
     <row r="70">
@@ -13967,13 +14009,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G70" t="n">
         <v>3.354</v>
       </c>
       <c r="H70" t="n">
-        <v>0.5</v>
+        <v>0.646</v>
       </c>
     </row>
     <row r="71">
@@ -13996,13 +14038,13 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G71" t="n">
         <v>2.865</v>
       </c>
       <c r="H71" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="72">
@@ -14025,13 +14067,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G72" t="n">
         <v>2.719</v>
       </c>
       <c r="H72" t="n">
-        <v>0.76</v>
+        <v>0.896</v>
       </c>
     </row>
     <row r="73">
@@ -14054,13 +14096,13 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G73" t="n">
         <v>2.698</v>
       </c>
       <c r="H73" t="n">
-        <v>0.76</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="74">
@@ -15067,13 +15109,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
         <v>2.427</v>
       </c>
       <c r="H10" t="n">
-        <v>0.427</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="11">
@@ -15096,13 +15138,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
         <v>2.312</v>
       </c>
       <c r="H11" t="n">
-        <v>0.469</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="12">
@@ -15125,13 +15167,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
         <v>2.25</v>
       </c>
       <c r="H12" t="n">
-        <v>0.49</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="13">
@@ -15154,13 +15196,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
         <v>2.354</v>
       </c>
       <c r="H13" t="n">
-        <v>0.573</v>
+        <v>0.646</v>
       </c>
     </row>
     <row r="14">
@@ -15183,13 +15225,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G14" t="n">
         <v>2.354</v>
       </c>
       <c r="H14" t="n">
-        <v>0.573</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -15212,13 +15254,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" t="n">
         <v>2.406</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.646</v>
       </c>
     </row>
     <row r="16">
@@ -15241,13 +15283,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
         <v>2.344</v>
       </c>
       <c r="H16" t="n">
-        <v>0.677</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="17">
@@ -15270,13 +15312,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G17" t="n">
         <v>2.396</v>
       </c>
       <c r="H17" t="n">
-        <v>0.646</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="18">
@@ -15995,13 +16037,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G42" t="n">
         <v>2.427</v>
       </c>
       <c r="H42" t="n">
-        <v>0.385</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="43">
@@ -16024,13 +16066,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G43" t="n">
         <v>2.312</v>
       </c>
       <c r="H43" t="n">
-        <v>0.427</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="44">
@@ -16053,13 +16095,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G44" t="n">
         <v>2.25</v>
       </c>
       <c r="H44" t="n">
-        <v>0.469</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="45">
@@ -16082,13 +16124,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G45" t="n">
         <v>2.354</v>
       </c>
       <c r="H45" t="n">
-        <v>0.552</v>
+        <v>0.646</v>
       </c>
     </row>
     <row r="46">
@@ -16111,13 +16153,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G46" t="n">
         <v>2.354</v>
       </c>
       <c r="H46" t="n">
-        <v>0.677</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -16140,13 +16182,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G47" t="n">
         <v>2.406</v>
       </c>
       <c r="H47" t="n">
-        <v>0.635</v>
+        <v>0.646</v>
       </c>
     </row>
     <row r="48">
@@ -16169,13 +16211,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G48" t="n">
         <v>2.344</v>
       </c>
       <c r="H48" t="n">
-        <v>0.729</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="49">
@@ -16198,13 +16240,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G49" t="n">
         <v>2.396</v>
       </c>
       <c r="H49" t="n">
-        <v>0.646</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="50">
@@ -16921,13 +16963,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
         <v>2.729</v>
       </c>
       <c r="H8" t="n">
-        <v>0.708</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="9">
@@ -16950,13 +16992,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
         <v>2.438</v>
       </c>
       <c r="H9" t="n">
-        <v>0.667</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="10">
@@ -16979,13 +17021,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" t="n">
         <v>2.74</v>
       </c>
       <c r="H10" t="n">
-        <v>0.865</v>
+        <v>1.104</v>
       </c>
     </row>
     <row r="11">
@@ -17008,13 +17050,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
         <v>3.021</v>
       </c>
       <c r="H11" t="n">
-        <v>0.583</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -17037,13 +17079,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
         <v>2.948</v>
       </c>
       <c r="H12" t="n">
-        <v>0.906</v>
+        <v>1.094</v>
       </c>
     </row>
     <row r="13">
@@ -17066,13 +17108,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
         <v>3.021</v>
       </c>
       <c r="H13" t="n">
-        <v>0.729</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="14">
@@ -17617,13 +17659,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
         <v>2.729</v>
       </c>
       <c r="H32" t="n">
-        <v>0.677</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="33">
@@ -17646,13 +17688,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
         <v>2.438</v>
       </c>
       <c r="H33" t="n">
-        <v>0.677</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="34">
@@ -17675,13 +17717,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G34" t="n">
         <v>2.74</v>
       </c>
       <c r="H34" t="n">
-        <v>0.917</v>
+        <v>1.104</v>
       </c>
     </row>
     <row r="35">
@@ -17704,13 +17746,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G35" t="n">
         <v>3.021</v>
       </c>
       <c r="H35" t="n">
-        <v>0.729</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -17733,13 +17775,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G36" t="n">
         <v>2.948</v>
       </c>
       <c r="H36" t="n">
-        <v>1.01</v>
+        <v>1.094</v>
       </c>
     </row>
     <row r="37">
@@ -17762,13 +17804,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G37" t="n">
         <v>3.021</v>
       </c>
       <c r="H37" t="n">
-        <v>0.823</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="38">
@@ -18130,7 +18172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:T41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19360,67 +19402,67 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>2.823</v>
+        <v>3.906</v>
       </c>
       <c r="F19" t="n">
-        <v>3.021</v>
+        <v>3.938</v>
       </c>
       <c r="G19" t="n">
-        <v>3.24</v>
+        <v>4.552</v>
       </c>
       <c r="H19" t="n">
-        <v>3.448</v>
+        <v>4.604</v>
       </c>
       <c r="I19" t="n">
-        <v>0.485</v>
+        <v>0.372</v>
       </c>
       <c r="J19" t="n">
-        <v>0.175</v>
+        <v>0.179</v>
       </c>
       <c r="K19" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.098</v>
       </c>
       <c r="L19" t="n">
-        <v>0.025</v>
+        <v>0.034</v>
       </c>
       <c r="M19" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.174</v>
       </c>
       <c r="N19" t="n">
-        <v>0.127</v>
+        <v>0.179</v>
       </c>
       <c r="O19" t="n">
-        <v>0.054</v>
+        <v>0.024</v>
       </c>
       <c r="P19" t="n">
-        <v>0.61</v>
+        <v>0.79</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.311</v>
+        <v>0.324</v>
       </c>
       <c r="R19" t="n">
-        <v>0.774</v>
+        <v>0.625</v>
       </c>
       <c r="S19" t="n">
-        <v>2.922</v>
+        <v>3.922</v>
       </c>
       <c r="T19" t="n">
-        <v>3.344</v>
+        <v>4.578</v>
       </c>
     </row>
     <row r="20">
@@ -19438,55 +19480,55 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>2.979</v>
+        <v>2.823</v>
       </c>
       <c r="F20" t="n">
-        <v>3.219</v>
+        <v>3.021</v>
       </c>
       <c r="G20" t="n">
-        <v>3.458</v>
+        <v>3.24</v>
       </c>
       <c r="H20" t="n">
-        <v>3.698</v>
+        <v>3.448</v>
       </c>
       <c r="I20" t="n">
-        <v>0.48</v>
+        <v>0.485</v>
       </c>
       <c r="J20" t="n">
-        <v>0.179</v>
+        <v>0.175</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="L20" t="n">
         <v>0.025</v>
       </c>
       <c r="M20" t="n">
-        <v>0.09</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>0.134</v>
+        <v>0.127</v>
       </c>
       <c r="O20" t="n">
-        <v>0.037</v>
+        <v>0.054</v>
       </c>
       <c r="P20" t="n">
-        <v>0.612</v>
+        <v>0.61</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.302</v>
+        <v>0.311</v>
       </c>
       <c r="R20" t="n">
-        <v>0.749</v>
+        <v>0.774</v>
       </c>
       <c r="S20" t="n">
-        <v>3.099</v>
+        <v>2.922</v>
       </c>
       <c r="T20" t="n">
-        <v>3.578</v>
+        <v>3.344</v>
       </c>
     </row>
     <row r="21">
@@ -19504,55 +19546,55 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>3.146</v>
+        <v>2.979</v>
       </c>
       <c r="F21" t="n">
-        <v>3.333</v>
+        <v>3.219</v>
       </c>
       <c r="G21" t="n">
-        <v>3.677</v>
+        <v>3.458</v>
       </c>
       <c r="H21" t="n">
-        <v>3.833</v>
+        <v>3.698</v>
       </c>
       <c r="I21" t="n">
-        <v>0.451</v>
+        <v>0.48</v>
       </c>
       <c r="J21" t="n">
-        <v>0.178</v>
+        <v>0.179</v>
       </c>
       <c r="K21" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="M21" t="n">
-        <v>0.112</v>
+        <v>0.09</v>
       </c>
       <c r="N21" t="n">
-        <v>0.168</v>
+        <v>0.134</v>
       </c>
       <c r="O21" t="n">
-        <v>0.046</v>
+        <v>0.037</v>
       </c>
       <c r="P21" t="n">
-        <v>0.764</v>
+        <v>0.612</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.291</v>
+        <v>0.302</v>
       </c>
       <c r="R21" t="n">
-        <v>0.708</v>
+        <v>0.749</v>
       </c>
       <c r="S21" t="n">
-        <v>3.24</v>
+        <v>3.099</v>
       </c>
       <c r="T21" t="n">
-        <v>3.755</v>
+        <v>3.578</v>
       </c>
     </row>
     <row r="22">
@@ -19570,55 +19612,55 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>3.365</v>
+        <v>3.146</v>
       </c>
       <c r="F22" t="n">
-        <v>3.573</v>
+        <v>3.333</v>
       </c>
       <c r="G22" t="n">
-        <v>3.927</v>
+        <v>3.677</v>
       </c>
       <c r="H22" t="n">
-        <v>4.01</v>
+        <v>3.833</v>
       </c>
       <c r="I22" t="n">
-        <v>0.48</v>
+        <v>0.451</v>
       </c>
       <c r="J22" t="n">
-        <v>0.171</v>
+        <v>0.178</v>
       </c>
       <c r="K22" t="n">
-        <v>0.089</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>0.031</v>
+        <v>0.03</v>
       </c>
       <c r="M22" t="n">
-        <v>0.128</v>
+        <v>0.112</v>
       </c>
       <c r="N22" t="n">
-        <v>0.17</v>
+        <v>0.168</v>
       </c>
       <c r="O22" t="n">
-        <v>0.027</v>
+        <v>0.046</v>
       </c>
       <c r="P22" t="n">
-        <v>0.673</v>
+        <v>0.764</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.318</v>
+        <v>0.291</v>
       </c>
       <c r="R22" t="n">
-        <v>0.675</v>
+        <v>0.708</v>
       </c>
       <c r="S22" t="n">
-        <v>3.469</v>
+        <v>3.24</v>
       </c>
       <c r="T22" t="n">
-        <v>3.969</v>
+        <v>3.755</v>
       </c>
     </row>
     <row r="23">
@@ -19636,55 +19678,55 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>3.552</v>
+        <v>3.365</v>
       </c>
       <c r="F23" t="n">
-        <v>3.708</v>
+        <v>3.573</v>
       </c>
       <c r="G23" t="n">
-        <v>4.24</v>
+        <v>3.927</v>
       </c>
       <c r="H23" t="n">
-        <v>4.198</v>
+        <v>4.01</v>
       </c>
       <c r="I23" t="n">
-        <v>0.451</v>
+        <v>0.48</v>
       </c>
       <c r="J23" t="n">
-        <v>0.152</v>
+        <v>0.171</v>
       </c>
       <c r="K23" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="L23" t="n">
-        <v>0.041</v>
+        <v>0.031</v>
       </c>
       <c r="M23" t="n">
-        <v>0.136</v>
+        <v>0.128</v>
       </c>
       <c r="N23" t="n">
-        <v>0.179</v>
+        <v>0.17</v>
       </c>
       <c r="O23" t="n">
-        <v>0.035</v>
+        <v>0.027</v>
       </c>
       <c r="P23" t="n">
-        <v>0.65</v>
+        <v>0.673</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.343</v>
+        <v>0.318</v>
       </c>
       <c r="R23" t="n">
-        <v>0.644</v>
+        <v>0.675</v>
       </c>
       <c r="S23" t="n">
-        <v>3.63</v>
+        <v>3.469</v>
       </c>
       <c r="T23" t="n">
-        <v>4.219</v>
+        <v>3.969</v>
       </c>
     </row>
     <row r="24">
@@ -19702,55 +19744,55 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>3.562</v>
+        <v>3.552</v>
       </c>
       <c r="F24" t="n">
-        <v>3.74</v>
+        <v>3.708</v>
       </c>
       <c r="G24" t="n">
-        <v>4.281</v>
+        <v>4.24</v>
       </c>
       <c r="H24" t="n">
-        <v>4.26</v>
+        <v>4.198</v>
       </c>
       <c r="I24" t="n">
-        <v>0.446</v>
+        <v>0.451</v>
       </c>
       <c r="J24" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="K24" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>0.037</v>
+        <v>0.041</v>
       </c>
       <c r="M24" t="n">
-        <v>0.148</v>
+        <v>0.136</v>
       </c>
       <c r="N24" t="n">
-        <v>0.198</v>
+        <v>0.179</v>
       </c>
       <c r="O24" t="n">
-        <v>0.029</v>
+        <v>0.035</v>
       </c>
       <c r="P24" t="n">
-        <v>0.607</v>
+        <v>0.65</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.32</v>
+        <v>0.343</v>
       </c>
       <c r="R24" t="n">
-        <v>0.622</v>
+        <v>0.644</v>
       </c>
       <c r="S24" t="n">
-        <v>3.651</v>
+        <v>3.63</v>
       </c>
       <c r="T24" t="n">
-        <v>4.271</v>
+        <v>4.219</v>
       </c>
     </row>
     <row r="25">
@@ -19768,55 +19810,55 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>3.729</v>
+        <v>3.562</v>
       </c>
       <c r="F25" t="n">
-        <v>3.781</v>
+        <v>3.74</v>
       </c>
       <c r="G25" t="n">
-        <v>4.427</v>
+        <v>4.281</v>
       </c>
       <c r="H25" t="n">
-        <v>4.427</v>
+        <v>4.26</v>
       </c>
       <c r="I25" t="n">
-        <v>0.498</v>
+        <v>0.446</v>
       </c>
       <c r="J25" t="n">
-        <v>0.159</v>
+        <v>0.153</v>
       </c>
       <c r="K25" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>0.065</v>
+        <v>0.037</v>
       </c>
       <c r="M25" t="n">
-        <v>0.149</v>
+        <v>0.148</v>
       </c>
       <c r="N25" t="n">
-        <v>0.209</v>
+        <v>0.198</v>
       </c>
       <c r="O25" t="n">
-        <v>0.053</v>
+        <v>0.029</v>
       </c>
       <c r="P25" t="n">
-        <v>0.652</v>
+        <v>0.607</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.324</v>
+        <v>0.32</v>
       </c>
       <c r="R25" t="n">
-        <v>0.645</v>
+        <v>0.622</v>
       </c>
       <c r="S25" t="n">
-        <v>3.755</v>
+        <v>3.651</v>
       </c>
       <c r="T25" t="n">
-        <v>4.427</v>
+        <v>4.271</v>
       </c>
     </row>
     <row r="26">
@@ -19834,55 +19876,55 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>3.688</v>
+        <v>3.729</v>
       </c>
       <c r="F26" t="n">
-        <v>3.76</v>
+        <v>3.781</v>
       </c>
       <c r="G26" t="n">
         <v>4.427</v>
       </c>
       <c r="H26" t="n">
-        <v>4.396</v>
+        <v>4.427</v>
       </c>
       <c r="I26" t="n">
-        <v>0.442</v>
+        <v>0.498</v>
       </c>
       <c r="J26" t="n">
-        <v>0.141</v>
+        <v>0.159</v>
       </c>
       <c r="K26" t="n">
-        <v>0.08</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.065</v>
       </c>
       <c r="M26" t="n">
-        <v>0.144</v>
+        <v>0.149</v>
       </c>
       <c r="N26" t="n">
-        <v>0.205</v>
+        <v>0.209</v>
       </c>
       <c r="O26" t="n">
-        <v>0.058</v>
+        <v>0.053</v>
       </c>
       <c r="P26" t="n">
-        <v>0.606</v>
+        <v>0.652</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.339</v>
+        <v>0.324</v>
       </c>
       <c r="R26" t="n">
-        <v>0.639</v>
+        <v>0.645</v>
       </c>
       <c r="S26" t="n">
-        <v>3.724</v>
+        <v>3.755</v>
       </c>
       <c r="T26" t="n">
-        <v>4.411</v>
+        <v>4.427</v>
       </c>
     </row>
     <row r="27">
@@ -19900,55 +19942,55 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>3.802</v>
+        <v>3.688</v>
       </c>
       <c r="F27" t="n">
-        <v>3.844</v>
+        <v>3.76</v>
       </c>
       <c r="G27" t="n">
-        <v>4.51</v>
+        <v>4.427</v>
       </c>
       <c r="H27" t="n">
-        <v>4.531</v>
+        <v>4.396</v>
       </c>
       <c r="I27" t="n">
-        <v>0.406</v>
+        <v>0.442</v>
       </c>
       <c r="J27" t="n">
-        <v>0.174</v>
+        <v>0.141</v>
       </c>
       <c r="K27" t="n">
-        <v>0.106</v>
+        <v>0.08</v>
       </c>
       <c r="L27" t="n">
-        <v>0.091</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>0.149</v>
+        <v>0.144</v>
       </c>
       <c r="N27" t="n">
-        <v>0.214</v>
+        <v>0.205</v>
       </c>
       <c r="O27" t="n">
-        <v>0.073</v>
+        <v>0.058</v>
       </c>
       <c r="P27" t="n">
-        <v>0.798</v>
+        <v>0.606</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.324</v>
+        <v>0.339</v>
       </c>
       <c r="R27" t="n">
-        <v>0.68</v>
+        <v>0.639</v>
       </c>
       <c r="S27" t="n">
-        <v>3.823</v>
+        <v>3.724</v>
       </c>
       <c r="T27" t="n">
-        <v>4.521</v>
+        <v>4.411</v>
       </c>
     </row>
     <row r="28">
@@ -19966,55 +20008,55 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>3.896</v>
+        <v>3.802</v>
       </c>
       <c r="F28" t="n">
-        <v>3.927</v>
+        <v>3.844</v>
       </c>
       <c r="G28" t="n">
-        <v>4.573</v>
+        <v>4.51</v>
       </c>
       <c r="H28" t="n">
-        <v>4.573</v>
+        <v>4.531</v>
       </c>
       <c r="I28" t="n">
-        <v>0.394</v>
+        <v>0.406</v>
       </c>
       <c r="J28" t="n">
-        <v>0.153</v>
+        <v>0.174</v>
       </c>
       <c r="K28" t="n">
-        <v>0.097</v>
+        <v>0.106</v>
       </c>
       <c r="L28" t="n">
-        <v>0.131</v>
+        <v>0.091</v>
       </c>
       <c r="M28" t="n">
-        <v>0.163</v>
+        <v>0.149</v>
       </c>
       <c r="N28" t="n">
-        <v>0.22</v>
+        <v>0.214</v>
       </c>
       <c r="O28" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.073</v>
       </c>
       <c r="P28" t="n">
-        <v>0.727</v>
+        <v>0.798</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.331</v>
+        <v>0.324</v>
       </c>
       <c r="R28" t="n">
-        <v>0.677</v>
+        <v>0.68</v>
       </c>
       <c r="S28" t="n">
-        <v>3.911</v>
+        <v>3.823</v>
       </c>
       <c r="T28" t="n">
-        <v>4.573</v>
+        <v>4.521</v>
       </c>
     </row>
     <row r="29">
@@ -20032,61 +20074,61 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>3.979</v>
+        <v>3.896</v>
       </c>
       <c r="F29" t="n">
-        <v>3.885</v>
+        <v>3.927</v>
       </c>
       <c r="G29" t="n">
-        <v>4.615</v>
+        <v>4.573</v>
       </c>
       <c r="H29" t="n">
-        <v>4.615</v>
+        <v>4.573</v>
       </c>
       <c r="I29" t="n">
-        <v>0.405</v>
+        <v>0.394</v>
       </c>
       <c r="J29" t="n">
         <v>0.153</v>
       </c>
       <c r="K29" t="n">
-        <v>0.105</v>
+        <v>0.097</v>
       </c>
       <c r="L29" t="n">
-        <v>0.142</v>
+        <v>0.131</v>
       </c>
       <c r="M29" t="n">
-        <v>0.15</v>
+        <v>0.163</v>
       </c>
       <c r="N29" t="n">
-        <v>0.226</v>
+        <v>0.22</v>
       </c>
       <c r="O29" t="n">
-        <v>0.074</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P29" t="n">
-        <v>0.75</v>
+        <v>0.727</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.364</v>
+        <v>0.331</v>
       </c>
       <c r="R29" t="n">
-        <v>0.7</v>
+        <v>0.677</v>
       </c>
       <c r="S29" t="n">
-        <v>3.932</v>
+        <v>3.911</v>
       </c>
       <c r="T29" t="n">
-        <v>4.615</v>
+        <v>4.573</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -20095,58 +20137,58 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>2.812</v>
+        <v>3.979</v>
       </c>
       <c r="F30" t="n">
-        <v>3.094</v>
+        <v>3.885</v>
       </c>
       <c r="G30" t="n">
-        <v>3.24</v>
+        <v>4.615</v>
       </c>
       <c r="H30" t="n">
-        <v>3.448</v>
+        <v>4.615</v>
       </c>
       <c r="I30" t="n">
-        <v>0.476</v>
+        <v>0.405</v>
       </c>
       <c r="J30" t="n">
-        <v>0.175</v>
+        <v>0.153</v>
       </c>
       <c r="K30" t="n">
-        <v>0.078</v>
+        <v>0.105</v>
       </c>
       <c r="L30" t="n">
-        <v>0.029</v>
+        <v>0.142</v>
       </c>
       <c r="M30" t="n">
-        <v>0.091</v>
+        <v>0.15</v>
       </c>
       <c r="N30" t="n">
-        <v>0.133</v>
+        <v>0.226</v>
       </c>
       <c r="O30" t="n">
-        <v>0.049</v>
+        <v>0.074</v>
       </c>
       <c r="P30" t="n">
-        <v>0.728</v>
+        <v>0.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.294</v>
+        <v>0.364</v>
       </c>
       <c r="R30" t="n">
-        <v>0.753</v>
+        <v>0.7</v>
       </c>
       <c r="S30" t="n">
-        <v>2.953</v>
+        <v>3.932</v>
       </c>
       <c r="T30" t="n">
-        <v>3.344</v>
+        <v>4.615</v>
       </c>
     </row>
     <row r="31">
@@ -20164,55 +20206,55 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>2.844</v>
+        <v>2.812</v>
       </c>
       <c r="F31" t="n">
-        <v>3.177</v>
+        <v>3.094</v>
       </c>
       <c r="G31" t="n">
-        <v>3.312</v>
+        <v>3.24</v>
       </c>
       <c r="H31" t="n">
-        <v>3.51</v>
+        <v>3.448</v>
       </c>
       <c r="I31" t="n">
-        <v>0.486</v>
+        <v>0.476</v>
       </c>
       <c r="J31" t="n">
-        <v>0.179</v>
+        <v>0.175</v>
       </c>
       <c r="K31" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.078</v>
       </c>
       <c r="L31" t="n">
-        <v>0.023</v>
+        <v>0.029</v>
       </c>
       <c r="M31" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.091</v>
       </c>
       <c r="N31" t="n">
-        <v>0.134</v>
+        <v>0.133</v>
       </c>
       <c r="O31" t="n">
-        <v>0.04</v>
+        <v>0.049</v>
       </c>
       <c r="P31" t="n">
-        <v>0.626</v>
+        <v>0.728</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.306</v>
+        <v>0.294</v>
       </c>
       <c r="R31" t="n">
-        <v>0.755</v>
+        <v>0.753</v>
       </c>
       <c r="S31" t="n">
-        <v>3.01</v>
+        <v>2.953</v>
       </c>
       <c r="T31" t="n">
-        <v>3.411</v>
+        <v>3.344</v>
       </c>
     </row>
     <row r="32">
@@ -20230,55 +20272,55 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.042</v>
+        <v>2.844</v>
       </c>
       <c r="F32" t="n">
-        <v>3.219</v>
+        <v>3.177</v>
       </c>
       <c r="G32" t="n">
-        <v>3.573</v>
+        <v>3.312</v>
       </c>
       <c r="H32" t="n">
-        <v>3.74</v>
+        <v>3.51</v>
       </c>
       <c r="I32" t="n">
-        <v>0.423</v>
+        <v>0.486</v>
       </c>
       <c r="J32" t="n">
-        <v>0.184</v>
+        <v>0.179</v>
       </c>
       <c r="K32" t="n">
-        <v>0.097</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>0.031</v>
+        <v>0.023</v>
       </c>
       <c r="M32" t="n">
-        <v>0.118</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>0.152</v>
+        <v>0.134</v>
       </c>
       <c r="O32" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="P32" t="n">
-        <v>0.764</v>
+        <v>0.626</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.342</v>
+        <v>0.306</v>
       </c>
       <c r="R32" t="n">
-        <v>0.72</v>
+        <v>0.755</v>
       </c>
       <c r="S32" t="n">
-        <v>3.13</v>
+        <v>3.01</v>
       </c>
       <c r="T32" t="n">
-        <v>3.656</v>
+        <v>3.411</v>
       </c>
     </row>
     <row r="33">
@@ -20296,55 +20338,55 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.25</v>
+        <v>3.042</v>
       </c>
       <c r="F33" t="n">
-        <v>3.469</v>
+        <v>3.219</v>
       </c>
       <c r="G33" t="n">
-        <v>3.792</v>
+        <v>3.573</v>
       </c>
       <c r="H33" t="n">
-        <v>3.938</v>
+        <v>3.74</v>
       </c>
       <c r="I33" t="n">
-        <v>0.454</v>
+        <v>0.423</v>
       </c>
       <c r="J33" t="n">
-        <v>0.161</v>
+        <v>0.184</v>
       </c>
       <c r="K33" t="n">
-        <v>0.092</v>
+        <v>0.097</v>
       </c>
       <c r="L33" t="n">
-        <v>0.026</v>
+        <v>0.031</v>
       </c>
       <c r="M33" t="n">
-        <v>0.123</v>
+        <v>0.118</v>
       </c>
       <c r="N33" t="n">
-        <v>0.16</v>
+        <v>0.152</v>
       </c>
       <c r="O33" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="P33" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.764</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.321</v>
+        <v>0.342</v>
       </c>
       <c r="R33" t="n">
-        <v>0.678</v>
+        <v>0.72</v>
       </c>
       <c r="S33" t="n">
-        <v>3.359</v>
+        <v>3.13</v>
       </c>
       <c r="T33" t="n">
-        <v>3.865</v>
+        <v>3.656</v>
       </c>
     </row>
     <row r="34">
@@ -20362,55 +20404,55 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F34" t="n">
         <v>3.469</v>
       </c>
-      <c r="F34" t="n">
-        <v>3.583</v>
-      </c>
       <c r="G34" t="n">
-        <v>4.021</v>
+        <v>3.792</v>
       </c>
       <c r="H34" t="n">
-        <v>4.146</v>
+        <v>3.938</v>
       </c>
       <c r="I34" t="n">
-        <v>0.444</v>
+        <v>0.454</v>
       </c>
       <c r="J34" t="n">
-        <v>0.137</v>
+        <v>0.161</v>
       </c>
       <c r="K34" t="n">
-        <v>0.078</v>
+        <v>0.092</v>
       </c>
       <c r="L34" t="n">
-        <v>0.032</v>
+        <v>0.026</v>
       </c>
       <c r="M34" t="n">
-        <v>0.144</v>
+        <v>0.123</v>
       </c>
       <c r="N34" t="n">
-        <v>0.186</v>
+        <v>0.16</v>
       </c>
       <c r="O34" t="n">
-        <v>0.049</v>
+        <v>0.034</v>
       </c>
       <c r="P34" t="n">
-        <v>0.589</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.317</v>
+        <v>0.321</v>
       </c>
       <c r="R34" t="n">
-        <v>0.62</v>
+        <v>0.678</v>
       </c>
       <c r="S34" t="n">
-        <v>3.526</v>
+        <v>3.359</v>
       </c>
       <c r="T34" t="n">
-        <v>4.083</v>
+        <v>3.865</v>
       </c>
     </row>
     <row r="35">
@@ -20428,55 +20470,55 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
+        <v>3.469</v>
+      </c>
+      <c r="F35" t="n">
         <v>3.583</v>
       </c>
-      <c r="F35" t="n">
-        <v>3.646</v>
-      </c>
       <c r="G35" t="n">
-        <v>4.198</v>
+        <v>4.021</v>
       </c>
       <c r="H35" t="n">
-        <v>4.292</v>
+        <v>4.146</v>
       </c>
       <c r="I35" t="n">
-        <v>0.437</v>
+        <v>0.444</v>
       </c>
       <c r="J35" t="n">
-        <v>0.145</v>
+        <v>0.137</v>
       </c>
       <c r="K35" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="L35" t="n">
-        <v>0.038</v>
+        <v>0.032</v>
       </c>
       <c r="M35" t="n">
-        <v>0.154</v>
+        <v>0.144</v>
       </c>
       <c r="N35" t="n">
-        <v>0.2</v>
+        <v>0.186</v>
       </c>
       <c r="O35" t="n">
-        <v>0.034</v>
+        <v>0.049</v>
       </c>
       <c r="P35" t="n">
-        <v>0.629</v>
+        <v>0.589</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.298</v>
+        <v>0.317</v>
       </c>
       <c r="R35" t="n">
-        <v>0.602</v>
+        <v>0.62</v>
       </c>
       <c r="S35" t="n">
-        <v>3.615</v>
+        <v>3.526</v>
       </c>
       <c r="T35" t="n">
-        <v>4.245</v>
+        <v>4.083</v>
       </c>
     </row>
     <row r="36">
@@ -20494,55 +20536,55 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>3.521</v>
+        <v>3.583</v>
       </c>
       <c r="F36" t="n">
+        <v>3.646</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4.198</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4.292</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="S36" t="n">
         <v>3.615</v>
       </c>
-      <c r="G36" t="n">
-        <v>4.167</v>
-      </c>
-      <c r="H36" t="n">
-        <v>4.219</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.044</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.166</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0.663</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0.297</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.568</v>
-      </c>
       <c r="T36" t="n">
-        <v>4.193</v>
+        <v>4.245</v>
       </c>
     </row>
     <row r="37">
@@ -20560,55 +20602,55 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>3.656</v>
+        <v>3.521</v>
       </c>
       <c r="F37" t="n">
-        <v>3.75</v>
+        <v>3.615</v>
       </c>
       <c r="G37" t="n">
-        <v>4.302</v>
+        <v>4.167</v>
       </c>
       <c r="H37" t="n">
-        <v>4.354</v>
+        <v>4.219</v>
       </c>
       <c r="I37" t="n">
-        <v>0.409</v>
+        <v>0.416</v>
       </c>
       <c r="J37" t="n">
-        <v>0.159</v>
+        <v>0.161</v>
       </c>
       <c r="K37" t="n">
-        <v>0.103</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>0.03</v>
+        <v>0.044</v>
       </c>
       <c r="M37" t="n">
-        <v>0.152</v>
+        <v>0.166</v>
       </c>
       <c r="N37" t="n">
-        <v>0.182</v>
+        <v>0.19</v>
       </c>
       <c r="O37" t="n">
-        <v>0.03</v>
+        <v>0.042</v>
       </c>
       <c r="P37" t="n">
-        <v>0.78</v>
+        <v>0.663</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.367</v>
+        <v>0.297</v>
       </c>
       <c r="R37" t="n">
-        <v>0.627</v>
+        <v>0.608</v>
       </c>
       <c r="S37" t="n">
-        <v>3.703</v>
+        <v>3.568</v>
       </c>
       <c r="T37" t="n">
-        <v>4.328</v>
+        <v>4.193</v>
       </c>
     </row>
     <row r="38">
@@ -20626,55 +20668,55 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>3.771</v>
+        <v>3.656</v>
       </c>
       <c r="F38" t="n">
-        <v>3.729</v>
+        <v>3.75</v>
       </c>
       <c r="G38" t="n">
-        <v>4.49</v>
+        <v>4.302</v>
       </c>
       <c r="H38" t="n">
-        <v>4.448</v>
+        <v>4.354</v>
       </c>
       <c r="I38" t="n">
-        <v>0.393</v>
+        <v>0.409</v>
       </c>
       <c r="J38" t="n">
         <v>0.159</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1</v>
+        <v>0.103</v>
       </c>
       <c r="L38" t="n">
-        <v>0.024</v>
+        <v>0.03</v>
       </c>
       <c r="M38" t="n">
-        <v>0.167</v>
+        <v>0.152</v>
       </c>
       <c r="N38" t="n">
-        <v>0.186</v>
+        <v>0.182</v>
       </c>
       <c r="O38" t="n">
-        <v>0.019</v>
+        <v>0.03</v>
       </c>
       <c r="P38" t="n">
-        <v>0.726</v>
+        <v>0.78</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.364</v>
+        <v>0.367</v>
       </c>
       <c r="R38" t="n">
-        <v>0.609</v>
+        <v>0.627</v>
       </c>
       <c r="S38" t="n">
-        <v>3.75</v>
+        <v>3.703</v>
       </c>
       <c r="T38" t="n">
-        <v>4.469</v>
+        <v>4.328</v>
       </c>
     </row>
     <row r="39">
@@ -20692,55 +20734,55 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>3.76</v>
+        <v>3.771</v>
       </c>
       <c r="F39" t="n">
-        <v>3.812</v>
+        <v>3.729</v>
       </c>
       <c r="G39" t="n">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="H39" t="n">
-        <v>4.542</v>
+        <v>4.448</v>
       </c>
       <c r="I39" t="n">
-        <v>0.384</v>
+        <v>0.393</v>
       </c>
       <c r="J39" t="n">
-        <v>0.173</v>
+        <v>0.159</v>
       </c>
       <c r="K39" t="n">
-        <v>0.108</v>
+        <v>0.1</v>
       </c>
       <c r="L39" t="n">
-        <v>0.047</v>
+        <v>0.024</v>
       </c>
       <c r="M39" t="n">
-        <v>0.157</v>
+        <v>0.167</v>
       </c>
       <c r="N39" t="n">
-        <v>0.175</v>
+        <v>0.186</v>
       </c>
       <c r="O39" t="n">
-        <v>0.039</v>
+        <v>0.019</v>
       </c>
       <c r="P39" t="n">
-        <v>0.873</v>
+        <v>0.726</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.357</v>
+        <v>0.364</v>
       </c>
       <c r="R39" t="n">
-        <v>0.659</v>
+        <v>0.609</v>
       </c>
       <c r="S39" t="n">
-        <v>3.786</v>
+        <v>3.75</v>
       </c>
       <c r="T39" t="n">
-        <v>4.521</v>
+        <v>4.469</v>
       </c>
     </row>
     <row r="40">
@@ -20758,54 +20800,120 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E40" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.812</v>
+      </c>
+      <c r="G40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4.542</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.786</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4.521</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="n">
         <v>3.938</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F41" t="n">
         <v>3.938</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G41" t="n">
         <v>4.583</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H41" t="n">
         <v>4.573</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I41" t="n">
         <v>0.376</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J41" t="n">
         <v>0.18</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K41" t="n">
         <v>0.116</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L41" t="n">
         <v>0.043</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M41" t="n">
         <v>0.156</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N41" t="n">
         <v>0.166</v>
       </c>
-      <c r="O40" t="n">
+      <c r="O41" t="n">
         <v>0.034</v>
       </c>
-      <c r="P40" t="n">
+      <c r="P41" t="n">
         <v>0.951</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q41" t="n">
         <v>0.369</v>
       </c>
-      <c r="R40" t="n">
+      <c r="R41" t="n">
         <v>0.664</v>
       </c>
-      <c r="S40" t="n">
+      <c r="S41" t="n">
         <v>3.938</v>
       </c>
-      <c r="T40" t="n">
+      <c r="T41" t="n">
         <v>4.578</v>
       </c>
     </row>
@@ -21383,13 +21491,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" t="n">
         <v>2.833</v>
       </c>
       <c r="H18" t="n">
-        <v>0.823</v>
+        <v>1.073</v>
       </c>
     </row>
     <row r="19">
@@ -21414,13 +21522,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G19" t="n">
         <v>3.042</v>
       </c>
       <c r="H19" t="n">
-        <v>0.646</v>
+        <v>0.896</v>
       </c>
     </row>
     <row r="20">
@@ -21445,13 +21553,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" t="n">
         <v>3.146</v>
       </c>
       <c r="H20" t="n">
-        <v>1.146</v>
+        <v>1.406</v>
       </c>
     </row>
     <row r="21">
@@ -21476,13 +21584,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G21" t="n">
         <v>3.458</v>
       </c>
       <c r="H21" t="n">
-        <v>0.948</v>
+        <v>1.146</v>
       </c>
     </row>
     <row r="22">
@@ -21507,13 +21615,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
         <v>0.471</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.099</v>
       </c>
     </row>
     <row r="23">
@@ -21538,13 +21646,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" t="n">
         <v>0.199</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.042</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="24">
@@ -21569,13 +21677,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="25">
@@ -21600,13 +21708,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G25" t="n">
         <v>0.026</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.005</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="26">
@@ -21631,13 +21739,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
         <v>0.078</v>
       </c>
       <c r="H26" t="n">
-        <v>0.11</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="27">
@@ -21662,13 +21770,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
         <v>0.119</v>
       </c>
       <c r="H27" t="n">
-        <v>0.092</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="28">
@@ -21693,13 +21801,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
         <v>0.038</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.019</v>
+        <v>-0.013</v>
       </c>
     </row>
     <row r="29">
@@ -21724,13 +21832,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
         <v>0.765</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.052</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="30">
@@ -21755,13 +21863,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G30" t="n">
         <v>0.276</v>
       </c>
       <c r="H30" t="n">
-        <v>0.024</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="31">
@@ -21786,13 +21894,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G31" t="n">
         <v>0.793</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.255</v>
+        <v>-0.168</v>
       </c>
     </row>
     <row r="32">
@@ -21817,13 +21925,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32" t="n">
         <v>2.938</v>
       </c>
       <c r="H32" t="n">
-        <v>0.734</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="33">
@@ -21848,13 +21956,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
         <v>3.302</v>
       </c>
       <c r="H33" t="n">
-        <v>1.047</v>
+        <v>1.276</v>
       </c>
     </row>
     <row r="34">
@@ -23367,13 +23475,13 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G82" t="n">
         <v>2.833</v>
       </c>
       <c r="H82" t="n">
-        <v>0.969</v>
+        <v>1.073</v>
       </c>
     </row>
     <row r="83">
@@ -23398,13 +23506,13 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G83" t="n">
         <v>3.042</v>
       </c>
       <c r="H83" t="n">
-        <v>0.781</v>
+        <v>0.896</v>
       </c>
     </row>
     <row r="84">
@@ -23429,13 +23537,13 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G84" t="n">
         <v>3.146</v>
       </c>
       <c r="H84" t="n">
-        <v>1.156</v>
+        <v>1.406</v>
       </c>
     </row>
     <row r="85">
@@ -23460,13 +23568,13 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G85" t="n">
         <v>3.458</v>
       </c>
       <c r="H85" t="n">
-        <v>0.948</v>
+        <v>1.146</v>
       </c>
     </row>
     <row r="86">
@@ -23491,13 +23599,13 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G86" t="n">
         <v>0.471</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.099</v>
       </c>
     </row>
     <row r="87">
@@ -23522,13 +23630,13 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G87" t="n">
         <v>0.199</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.035</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="88">
@@ -23553,13 +23661,13 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G88" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="89">
@@ -23584,13 +23692,13 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G89" t="n">
         <v>0.026</v>
       </c>
       <c r="H89" t="n">
-        <v>0.012</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="90">
@@ -23615,13 +23723,13 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G90" t="n">
         <v>0.078</v>
       </c>
       <c r="H90" t="n">
-        <v>0.083</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="91">
@@ -23646,13 +23754,13 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G91" t="n">
         <v>0.119</v>
       </c>
       <c r="H91" t="n">
-        <v>0.073</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="92">
@@ -23677,13 +23785,13 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G92" t="n">
         <v>0.038</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.011</v>
+        <v>-0.013</v>
       </c>
     </row>
     <row r="93">
@@ -23708,13 +23816,13 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G93" t="n">
         <v>0.765</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="94">
@@ -23739,13 +23847,13 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G94" t="n">
         <v>0.276</v>
       </c>
       <c r="H94" t="n">
-        <v>0.066</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="95">
@@ -23770,13 +23878,13 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G95" t="n">
         <v>0.793</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.17</v>
+        <v>-0.168</v>
       </c>
     </row>
     <row r="96">
@@ -23801,13 +23909,13 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G96" t="n">
         <v>2.938</v>
       </c>
       <c r="H96" t="n">
-        <v>0.875</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="97">
@@ -23832,13 +23940,13 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G97" t="n">
         <v>3.302</v>
       </c>
       <c r="H97" t="n">
-        <v>1.052</v>
+        <v>1.276</v>
       </c>
     </row>
     <row r="98">
@@ -24983,27 +25091,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>final (iter 5)</t>
+          <t>final (iter 6)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.71 ✗</t>
+          <t>0.79 ✗</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.30 ✗</t>
+          <t>0.32 ✗</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.67 ✓fair</t>
+          <t>3.92 ✓fair</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4.35 ✓good</t>
+          <t>4.58 ✓good</t>
         </is>
       </c>
     </row>
@@ -25146,7 +25254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25928,43 +26036,43 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>3.427</v>
+        <v>3.885</v>
       </c>
       <c r="F19" t="n">
-        <v>2.719</v>
+        <v>3.208</v>
       </c>
       <c r="G19" t="n">
-        <v>3.083</v>
+        <v>3.875</v>
       </c>
       <c r="H19" t="n">
-        <v>3.076</v>
+        <v>3.656</v>
       </c>
       <c r="I19" t="n">
-        <v>0.489</v>
+        <v>0.625</v>
       </c>
       <c r="J19" t="n">
-        <v>0.419</v>
+        <v>0.547</v>
       </c>
       <c r="K19" t="n">
-        <v>0.43</v>
+        <v>0.325</v>
       </c>
       <c r="L19" t="n">
-        <v>0.151</v>
+        <v>0.128</v>
       </c>
     </row>
     <row r="20">
@@ -25982,31 +26090,31 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>3.396</v>
+        <v>3.427</v>
       </c>
       <c r="F20" t="n">
-        <v>2.75</v>
+        <v>2.719</v>
       </c>
       <c r="G20" t="n">
-        <v>3.073</v>
+        <v>3.083</v>
       </c>
       <c r="H20" t="n">
-        <v>3.073</v>
+        <v>3.076</v>
       </c>
       <c r="I20" t="n">
-        <v>0.459</v>
+        <v>0.489</v>
       </c>
       <c r="J20" t="n">
-        <v>0.39</v>
+        <v>0.419</v>
       </c>
       <c r="K20" t="n">
-        <v>0.459</v>
+        <v>0.43</v>
       </c>
       <c r="L20" t="n">
-        <v>0.152</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="21">
@@ -26024,31 +26132,31 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>3.458</v>
+        <v>3.396</v>
       </c>
       <c r="F21" t="n">
-        <v>2.854</v>
+        <v>2.75</v>
       </c>
       <c r="G21" t="n">
-        <v>3.229</v>
+        <v>3.073</v>
       </c>
       <c r="H21" t="n">
-        <v>3.181</v>
+        <v>3.073</v>
       </c>
       <c r="I21" t="n">
-        <v>0.491</v>
+        <v>0.459</v>
       </c>
       <c r="J21" t="n">
-        <v>0.416</v>
+        <v>0.39</v>
       </c>
       <c r="K21" t="n">
-        <v>0.428</v>
+        <v>0.459</v>
       </c>
       <c r="L21" t="n">
-        <v>0.156</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="22">
@@ -26066,31 +26174,31 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>3.479</v>
+        <v>3.458</v>
       </c>
       <c r="F22" t="n">
-        <v>2.906</v>
+        <v>2.854</v>
       </c>
       <c r="G22" t="n">
-        <v>3.406</v>
+        <v>3.229</v>
       </c>
       <c r="H22" t="n">
-        <v>3.264</v>
+        <v>3.181</v>
       </c>
       <c r="I22" t="n">
-        <v>0.533</v>
+        <v>0.491</v>
       </c>
       <c r="J22" t="n">
-        <v>0.469</v>
+        <v>0.416</v>
       </c>
       <c r="K22" t="n">
-        <v>0.403</v>
+        <v>0.428</v>
       </c>
       <c r="L22" t="n">
-        <v>0.127</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="23">
@@ -26108,31 +26216,31 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>3.594</v>
+        <v>3.479</v>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>2.906</v>
       </c>
       <c r="G23" t="n">
-        <v>3.51</v>
+        <v>3.406</v>
       </c>
       <c r="H23" t="n">
-        <v>3.368</v>
+        <v>3.264</v>
       </c>
       <c r="I23" t="n">
-        <v>0.538</v>
+        <v>0.533</v>
       </c>
       <c r="J23" t="n">
-        <v>0.465</v>
+        <v>0.469</v>
       </c>
       <c r="K23" t="n">
-        <v>0.404</v>
+        <v>0.403</v>
       </c>
       <c r="L23" t="n">
-        <v>0.131</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="24">
@@ -26150,31 +26258,31 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>3.542</v>
+        <v>3.594</v>
       </c>
       <c r="F24" t="n">
-        <v>2.969</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
         <v>3.51</v>
       </c>
       <c r="H24" t="n">
-        <v>3.34</v>
+        <v>3.368</v>
       </c>
       <c r="I24" t="n">
-        <v>0.555</v>
+        <v>0.538</v>
       </c>
       <c r="J24" t="n">
-        <v>0.478</v>
+        <v>0.465</v>
       </c>
       <c r="K24" t="n">
-        <v>0.387</v>
+        <v>0.404</v>
       </c>
       <c r="L24" t="n">
-        <v>0.135</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="25">
@@ -26192,31 +26300,31 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>3.688</v>
+        <v>3.542</v>
       </c>
       <c r="F25" t="n">
-        <v>3.052</v>
+        <v>2.969</v>
       </c>
       <c r="G25" t="n">
-        <v>3.667</v>
+        <v>3.51</v>
       </c>
       <c r="H25" t="n">
-        <v>3.469</v>
+        <v>3.34</v>
       </c>
       <c r="I25" t="n">
-        <v>0.569</v>
+        <v>0.555</v>
       </c>
       <c r="J25" t="n">
-        <v>0.507</v>
+        <v>0.478</v>
       </c>
       <c r="K25" t="n">
-        <v>0.376</v>
+        <v>0.387</v>
       </c>
       <c r="L25" t="n">
-        <v>0.117</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="26">
@@ -26234,31 +26342,31 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>3.562</v>
+        <v>3.688</v>
       </c>
       <c r="F26" t="n">
-        <v>2.969</v>
+        <v>3.052</v>
       </c>
       <c r="G26" t="n">
-        <v>3.531</v>
+        <v>3.667</v>
       </c>
       <c r="H26" t="n">
-        <v>3.354</v>
+        <v>3.469</v>
       </c>
       <c r="I26" t="n">
-        <v>0.545</v>
+        <v>0.569</v>
       </c>
       <c r="J26" t="n">
-        <v>0.477</v>
+        <v>0.507</v>
       </c>
       <c r="K26" t="n">
-        <v>0.399</v>
+        <v>0.376</v>
       </c>
       <c r="L26" t="n">
-        <v>0.124</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="27">
@@ -26276,31 +26384,31 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>3.688</v>
+        <v>3.562</v>
       </c>
       <c r="F27" t="n">
-        <v>3.073</v>
+        <v>2.969</v>
       </c>
       <c r="G27" t="n">
-        <v>3.688</v>
+        <v>3.531</v>
       </c>
       <c r="H27" t="n">
-        <v>3.483</v>
+        <v>3.354</v>
       </c>
       <c r="I27" t="n">
-        <v>0.573</v>
+        <v>0.545</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5</v>
+        <v>0.477</v>
       </c>
       <c r="K27" t="n">
-        <v>0.379</v>
+        <v>0.399</v>
       </c>
       <c r="L27" t="n">
-        <v>0.121</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="28">
@@ -26318,31 +26426,31 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>3.76</v>
+        <v>3.688</v>
       </c>
       <c r="F28" t="n">
-        <v>3.156</v>
+        <v>3.073</v>
       </c>
       <c r="G28" t="n">
-        <v>3.833</v>
+        <v>3.688</v>
       </c>
       <c r="H28" t="n">
-        <v>3.583</v>
+        <v>3.483</v>
       </c>
       <c r="I28" t="n">
-        <v>0.612</v>
+        <v>0.573</v>
       </c>
       <c r="J28" t="n">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>0.335</v>
+        <v>0.379</v>
       </c>
       <c r="L28" t="n">
-        <v>0.12</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="29">
@@ -26360,37 +26468,37 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" t="n">
-        <v>3.802</v>
+        <v>3.76</v>
       </c>
       <c r="F29" t="n">
-        <v>3.177</v>
+        <v>3.156</v>
       </c>
       <c r="G29" t="n">
         <v>3.833</v>
       </c>
       <c r="H29" t="n">
-        <v>3.604</v>
+        <v>3.583</v>
       </c>
       <c r="I29" t="n">
-        <v>0.63</v>
+        <v>0.612</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.545</v>
       </c>
       <c r="K29" t="n">
-        <v>0.327</v>
+        <v>0.335</v>
       </c>
       <c r="L29" t="n">
-        <v>0.113</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -26399,34 +26507,34 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>3.354</v>
+        <v>3.802</v>
       </c>
       <c r="F30" t="n">
-        <v>2.708</v>
+        <v>3.177</v>
       </c>
       <c r="G30" t="n">
-        <v>3.146</v>
+        <v>3.833</v>
       </c>
       <c r="H30" t="n">
-        <v>3.069</v>
+        <v>3.604</v>
       </c>
       <c r="I30" t="n">
-        <v>0.481</v>
+        <v>0.63</v>
       </c>
       <c r="J30" t="n">
-        <v>0.406</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.442</v>
+        <v>0.327</v>
       </c>
       <c r="L30" t="n">
-        <v>0.152</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="31">
@@ -26444,31 +26552,31 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>3.406</v>
+        <v>3.354</v>
       </c>
       <c r="F31" t="n">
-        <v>2.792</v>
+        <v>2.708</v>
       </c>
       <c r="G31" t="n">
-        <v>3.031</v>
+        <v>3.146</v>
       </c>
       <c r="H31" t="n">
-        <v>3.076</v>
+        <v>3.069</v>
       </c>
       <c r="I31" t="n">
-        <v>0.487</v>
+        <v>0.481</v>
       </c>
       <c r="J31" t="n">
-        <v>0.412</v>
+        <v>0.406</v>
       </c>
       <c r="K31" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L31" t="n">
-        <v>0.147</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="32">
@@ -26486,31 +26594,31 @@
         <v>5</v>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.448</v>
+        <v>3.406</v>
       </c>
       <c r="F32" t="n">
-        <v>2.812</v>
+        <v>2.792</v>
       </c>
       <c r="G32" t="n">
-        <v>3.26</v>
+        <v>3.031</v>
       </c>
       <c r="H32" t="n">
-        <v>3.174</v>
+        <v>3.076</v>
       </c>
       <c r="I32" t="n">
-        <v>0.495</v>
+        <v>0.487</v>
       </c>
       <c r="J32" t="n">
-        <v>0.425</v>
+        <v>0.412</v>
       </c>
       <c r="K32" t="n">
-        <v>0.43</v>
+        <v>0.441</v>
       </c>
       <c r="L32" t="n">
-        <v>0.145</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="33">
@@ -26528,31 +26636,31 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.646</v>
+        <v>3.448</v>
       </c>
       <c r="F33" t="n">
-        <v>2.969</v>
+        <v>2.812</v>
       </c>
       <c r="G33" t="n">
-        <v>3.479</v>
+        <v>3.26</v>
       </c>
       <c r="H33" t="n">
-        <v>3.365</v>
+        <v>3.174</v>
       </c>
       <c r="I33" t="n">
-        <v>0.531</v>
+        <v>0.495</v>
       </c>
       <c r="J33" t="n">
-        <v>0.454</v>
+        <v>0.425</v>
       </c>
       <c r="K33" t="n">
-        <v>0.394</v>
+        <v>0.43</v>
       </c>
       <c r="L33" t="n">
-        <v>0.152</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="34">
@@ -26570,31 +26678,31 @@
         <v>5</v>
       </c>
       <c r="D34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.719</v>
+        <v>3.646</v>
       </c>
       <c r="F34" t="n">
-        <v>3.021</v>
+        <v>2.969</v>
       </c>
       <c r="G34" t="n">
-        <v>3.635</v>
+        <v>3.479</v>
       </c>
       <c r="H34" t="n">
-        <v>3.458</v>
+        <v>3.365</v>
       </c>
       <c r="I34" t="n">
-        <v>0.556</v>
+        <v>0.531</v>
       </c>
       <c r="J34" t="n">
-        <v>0.488</v>
+        <v>0.454</v>
       </c>
       <c r="K34" t="n">
-        <v>0.385</v>
+        <v>0.394</v>
       </c>
       <c r="L34" t="n">
-        <v>0.127</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="35">
@@ -26612,31 +26720,31 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E35" t="n">
-        <v>3.729</v>
+        <v>3.719</v>
       </c>
       <c r="F35" t="n">
-        <v>3.042</v>
+        <v>3.021</v>
       </c>
       <c r="G35" t="n">
-        <v>3.667</v>
+        <v>3.635</v>
       </c>
       <c r="H35" t="n">
-        <v>3.479</v>
+        <v>3.458</v>
       </c>
       <c r="I35" t="n">
-        <v>0.575</v>
+        <v>0.556</v>
       </c>
       <c r="J35" t="n">
-        <v>0.506</v>
+        <v>0.488</v>
       </c>
       <c r="K35" t="n">
-        <v>0.377</v>
+        <v>0.385</v>
       </c>
       <c r="L35" t="n">
-        <v>0.116</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="36">
@@ -26654,31 +26762,31 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>3.688</v>
+        <v>3.729</v>
       </c>
       <c r="F36" t="n">
-        <v>3.062</v>
+        <v>3.042</v>
       </c>
       <c r="G36" t="n">
-        <v>3.625</v>
+        <v>3.667</v>
       </c>
       <c r="H36" t="n">
-        <v>3.458</v>
+        <v>3.479</v>
       </c>
       <c r="I36" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.575</v>
       </c>
       <c r="J36" t="n">
-        <v>0.493</v>
+        <v>0.506</v>
       </c>
       <c r="K36" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="L36" t="n">
-        <v>0.133</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="37">
@@ -26696,31 +26804,31 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" t="n">
-        <v>3.75</v>
+        <v>3.688</v>
       </c>
       <c r="F37" t="n">
-        <v>3.115</v>
+        <v>3.062</v>
       </c>
       <c r="G37" t="n">
-        <v>3.729</v>
+        <v>3.625</v>
       </c>
       <c r="H37" t="n">
-        <v>3.531</v>
+        <v>3.458</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>0.499</v>
+        <v>0.493</v>
       </c>
       <c r="K37" t="n">
-        <v>0.375</v>
+        <v>0.374</v>
       </c>
       <c r="L37" t="n">
-        <v>0.125</v>
+        <v>0.133</v>
       </c>
     </row>
     <row r="38">
@@ -26738,31 +26846,31 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E38" t="n">
-        <v>3.719</v>
+        <v>3.75</v>
       </c>
       <c r="F38" t="n">
-        <v>3.156</v>
+        <v>3.115</v>
       </c>
       <c r="G38" t="n">
-        <v>3.812</v>
+        <v>3.729</v>
       </c>
       <c r="H38" t="n">
-        <v>3.562</v>
+        <v>3.531</v>
       </c>
       <c r="I38" t="n">
-        <v>0.587</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>0.512</v>
+        <v>0.499</v>
       </c>
       <c r="K38" t="n">
-        <v>0.356</v>
+        <v>0.375</v>
       </c>
       <c r="L38" t="n">
-        <v>0.132</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="39">
@@ -26780,31 +26888,31 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>3.844</v>
+        <v>3.719</v>
       </c>
       <c r="F39" t="n">
-        <v>3.146</v>
+        <v>3.156</v>
       </c>
       <c r="G39" t="n">
-        <v>3.76</v>
+        <v>3.812</v>
       </c>
       <c r="H39" t="n">
-        <v>3.583</v>
+        <v>3.562</v>
       </c>
       <c r="I39" t="n">
-        <v>0.594</v>
+        <v>0.587</v>
       </c>
       <c r="J39" t="n">
-        <v>0.523</v>
+        <v>0.512</v>
       </c>
       <c r="K39" t="n">
-        <v>0.347</v>
+        <v>0.356</v>
       </c>
       <c r="L39" t="n">
-        <v>0.131</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="40">
@@ -26822,30 +26930,72 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E40" t="n">
+        <v>3.844</v>
+      </c>
+      <c r="F40" t="n">
+        <v>3.146</v>
+      </c>
+      <c r="G40" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3.583</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.131</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="n">
         <v>3.958</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F41" t="n">
         <v>3.229</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G41" t="n">
         <v>3.958</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H41" t="n">
         <v>3.715</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I41" t="n">
         <v>0.638</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J41" t="n">
         <v>0.5679999999999999</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K41" t="n">
         <v>0.315</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L41" t="n">
         <v>0.117</v>
       </c>
     </row>

--- a/Exp3_PTO_GRPO/eda/results/arms/questionnaires/tables/gpt-4o-mini/questionnaires.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/arms/questionnaires/tables/gpt-4o-mini/questionnaires.xlsx
@@ -634,13 +634,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
         <v>2.938</v>
       </c>
       <c r="H7" t="n">
-        <v>1.125</v>
+        <v>1.302</v>
       </c>
     </row>
     <row r="8">
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
         <v>2.927</v>
       </c>
       <c r="H8" t="n">
-        <v>1.135</v>
+        <v>1.385</v>
       </c>
     </row>
     <row r="9">
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
         <v>2.979</v>
       </c>
       <c r="H9" t="n">
-        <v>1.292</v>
+        <v>1.552</v>
       </c>
     </row>
     <row r="10">
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
         <v>2.667</v>
       </c>
       <c r="H10" t="n">
-        <v>1.531</v>
+        <v>1.865</v>
       </c>
     </row>
     <row r="11">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
         <v>3.042</v>
       </c>
       <c r="H11" t="n">
-        <v>1.365</v>
+        <v>1.667</v>
       </c>
     </row>
     <row r="12">
@@ -1214,13 +1214,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
         <v>2.938</v>
       </c>
       <c r="H27" t="n">
-        <v>1.125</v>
+        <v>1.302</v>
       </c>
     </row>
     <row r="28">
@@ -1243,13 +1243,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
         <v>2.927</v>
       </c>
       <c r="H28" t="n">
-        <v>1.135</v>
+        <v>1.385</v>
       </c>
     </row>
     <row r="29">
@@ -1272,13 +1272,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G29" t="n">
         <v>2.979</v>
       </c>
       <c r="H29" t="n">
-        <v>1.292</v>
+        <v>1.552</v>
       </c>
     </row>
     <row r="30">
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
         <v>2.667</v>
       </c>
       <c r="H30" t="n">
-        <v>1.531</v>
+        <v>1.865</v>
       </c>
     </row>
     <row r="31">
@@ -1330,13 +1330,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G31" t="n">
         <v>3.042</v>
       </c>
       <c r="H31" t="n">
-        <v>1.365</v>
+        <v>1.667</v>
       </c>
     </row>
     <row r="32">
@@ -1924,13 +1924,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
         <v>3.323</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.771</v>
       </c>
     </row>
     <row r="10">
@@ -1955,13 +1955,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
         <v>2.729</v>
       </c>
       <c r="H10" t="n">
-        <v>0.479</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="11">
@@ -1986,13 +1986,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
         <v>3.062</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8120000000000001</v>
+        <v>1.042</v>
       </c>
     </row>
     <row r="12">
@@ -2017,13 +2017,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
         <v>0.471</v>
       </c>
       <c r="H12" t="n">
-        <v>0.154</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="13">
@@ -2048,13 +2048,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
         <v>0.395</v>
       </c>
       <c r="H13" t="n">
-        <v>0.152</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="14">
@@ -2079,13 +2079,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
         <v>0.446</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.121</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="15">
@@ -2110,13 +2110,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
         <v>0.159</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.031</v>
+        <v>-0.052</v>
       </c>
     </row>
     <row r="16">
@@ -2792,13 +2792,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G37" t="n">
         <v>3.323</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.771</v>
       </c>
     </row>
     <row r="38">
@@ -2823,13 +2823,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G38" t="n">
         <v>2.729</v>
       </c>
       <c r="H38" t="n">
-        <v>0.479</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="39">
@@ -2854,13 +2854,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G39" t="n">
         <v>3.062</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8120000000000001</v>
+        <v>1.042</v>
       </c>
     </row>
     <row r="40">
@@ -2885,13 +2885,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G40" t="n">
         <v>0.471</v>
       </c>
       <c r="H40" t="n">
-        <v>0.154</v>
+        <v>0.214</v>
       </c>
     </row>
     <row r="41">
@@ -2916,13 +2916,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G41" t="n">
         <v>0.395</v>
       </c>
       <c r="H41" t="n">
-        <v>0.152</v>
+        <v>0.222</v>
       </c>
     </row>
     <row r="42">
@@ -2947,13 +2947,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G42" t="n">
         <v>0.446</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.121</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="43">
@@ -2978,13 +2978,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G43" t="n">
         <v>0.159</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.031</v>
+        <v>-0.052</v>
       </c>
     </row>
     <row r="44">
@@ -3432,7 +3432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4256,169 +4256,169 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.604</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3.458</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.213</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.006</v>
-      </c>
       <c r="J20" t="n">
-        <v>0.059</v>
+        <v>0.036</v>
       </c>
       <c r="K20" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.013</v>
+        <v>0.057</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="I21" t="n">
         <v>0</v>
       </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.209</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.126</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.005</v>
-      </c>
       <c r="J21" t="n">
-        <v>0.041</v>
+        <v>0.026</v>
       </c>
       <c r="K21" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="L21" t="n">
-        <v>0.029</v>
+        <v>0.052</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="I22" t="n">
         <v>0</v>
       </c>
-      <c r="D22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>3</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="J22" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="K22" t="n">
         <v>0.004</v>
       </c>
-      <c r="H22" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.033</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.005</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.017</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C23" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.479</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="D23" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.252</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.001</v>
-      </c>
       <c r="H23" t="n">
-        <v>0.174</v>
+        <v>0.119</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L23" t="n">
         <v>0.051</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0.026</v>
       </c>
     </row>
     <row r="24">
@@ -4436,31 +4436,31 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>2.406</v>
+        <v>3.458</v>
       </c>
       <c r="F24" t="n">
-        <v>0.215</v>
+        <v>0.213</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.007</v>
       </c>
       <c r="H24" t="n">
-        <v>0.142</v>
+        <v>0.121</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="J24" t="n">
-        <v>0.038</v>
+        <v>0.059</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="L24" t="n">
-        <v>0.034</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="25">
@@ -4478,31 +4478,31 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>2.594</v>
+        <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>0.289</v>
+        <v>0.209</v>
       </c>
       <c r="G25" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H25" t="n">
-        <v>0.188</v>
+        <v>0.126</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="J25" t="n">
-        <v>0.057</v>
+        <v>0.041</v>
       </c>
       <c r="K25" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="L25" t="n">
-        <v>0.037</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="26">
@@ -4520,31 +4520,31 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>2.531</v>
+        <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>0.318</v>
+        <v>0.22</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="H26" t="n">
-        <v>0.189</v>
+        <v>0.159</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="J26" t="n">
-        <v>0.051</v>
+        <v>0.033</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="L26" t="n">
-        <v>0.077</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="27">
@@ -4562,31 +4562,31 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>2.479</v>
+        <v>2.667</v>
       </c>
       <c r="F27" t="n">
-        <v>0.341</v>
+        <v>0.252</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.167</v>
+        <v>0.174</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.045</v>
+        <v>0.051</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.129</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="28">
@@ -4604,31 +4604,31 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>2.385</v>
+        <v>2.406</v>
       </c>
       <c r="F28" t="n">
-        <v>0.349</v>
+        <v>0.215</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.161</v>
+        <v>0.142</v>
       </c>
       <c r="I28" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.031</v>
+        <v>0.038</v>
       </c>
       <c r="K28" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0.154</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="29">
@@ -4646,31 +4646,31 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>2.625</v>
+        <v>2.594</v>
       </c>
       <c r="F29" t="n">
-        <v>0.471</v>
+        <v>0.289</v>
       </c>
       <c r="G29" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H29" t="n">
-        <v>0.165</v>
+        <v>0.188</v>
       </c>
       <c r="I29" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.033</v>
+        <v>0.057</v>
       </c>
       <c r="K29" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="L29" t="n">
-        <v>0.27</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="30">
@@ -4688,37 +4688,37 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>2.635</v>
+        <v>2.531</v>
       </c>
       <c r="F30" t="n">
-        <v>0.491</v>
+        <v>0.318</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.163</v>
+        <v>0.189</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0.03</v>
+        <v>0.051</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.299</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4727,40 +4727,40 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
+        <v>7</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2.479</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="G31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.004</v>
-      </c>
       <c r="H31" t="n">
-        <v>0.109</v>
+        <v>0.167</v>
       </c>
       <c r="I31" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.044</v>
+        <v>0.045</v>
       </c>
       <c r="K31" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.008</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4769,40 +4769,40 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>3.25</v>
+        <v>2.385</v>
       </c>
       <c r="F32" t="n">
-        <v>0.222</v>
+        <v>0.349</v>
       </c>
       <c r="G32" t="n">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.139</v>
+        <v>0.161</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J32" t="n">
-        <v>0.047</v>
+        <v>0.031</v>
       </c>
       <c r="K32" t="n">
         <v>0.002</v>
       </c>
       <c r="L32" t="n">
-        <v>0.031</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4811,40 +4811,40 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>3.188</v>
+        <v>2.625</v>
       </c>
       <c r="F33" t="n">
-        <v>0.231</v>
+        <v>0.471</v>
       </c>
       <c r="G33" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.141</v>
+        <v>0.165</v>
       </c>
       <c r="I33" t="n">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="J33" t="n">
-        <v>0.058</v>
+        <v>0.033</v>
       </c>
       <c r="K33" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="L33" t="n">
-        <v>0.017</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4853,34 +4853,34 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>2.938</v>
+        <v>2.635</v>
       </c>
       <c r="F34" t="n">
-        <v>0.248</v>
+        <v>0.491</v>
       </c>
       <c r="G34" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.17</v>
+        <v>0.163</v>
       </c>
       <c r="I34" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0.046</v>
+        <v>0.03</v>
       </c>
       <c r="K34" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.028</v>
+        <v>0.299</v>
       </c>
     </row>
     <row r="35">
@@ -4898,31 +4898,31 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>2.854</v>
+        <v>3.24</v>
       </c>
       <c r="F35" t="n">
-        <v>0.326</v>
+        <v>0.178</v>
       </c>
       <c r="G35" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="H35" t="n">
-        <v>0.21</v>
+        <v>0.109</v>
       </c>
       <c r="I35" t="n">
         <v>0.002</v>
       </c>
       <c r="J35" t="n">
-        <v>0.063</v>
+        <v>0.044</v>
       </c>
       <c r="K35" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
       <c r="L35" t="n">
-        <v>0.043</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="36">
@@ -4940,31 +4940,31 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>2.875</v>
+        <v>3.25</v>
       </c>
       <c r="F36" t="n">
-        <v>0.325</v>
+        <v>0.222</v>
       </c>
       <c r="G36" t="n">
         <v>0.004</v>
       </c>
       <c r="H36" t="n">
-        <v>0.224</v>
+        <v>0.139</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.062</v>
+        <v>0.047</v>
       </c>
       <c r="K36" t="n">
         <v>0.002</v>
       </c>
       <c r="L36" t="n">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="37">
@@ -4982,31 +4982,31 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>3.01</v>
+        <v>3.188</v>
       </c>
       <c r="F37" t="n">
-        <v>0.32</v>
+        <v>0.231</v>
       </c>
       <c r="G37" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.003</v>
       </c>
-      <c r="H37" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.002</v>
-      </c>
       <c r="J37" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.058</v>
       </c>
       <c r="K37" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="L37" t="n">
-        <v>0.036</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="38">
@@ -5024,31 +5024,31 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>2.719</v>
+        <v>2.938</v>
       </c>
       <c r="F38" t="n">
-        <v>0.263</v>
+        <v>0.248</v>
       </c>
       <c r="G38" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="J38" t="n">
-        <v>0.041</v>
+        <v>0.046</v>
       </c>
       <c r="K38" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="L38" t="n">
-        <v>0.033</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="39">
@@ -5066,31 +5066,31 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>2.865</v>
+        <v>2.854</v>
       </c>
       <c r="F39" t="n">
-        <v>0.29</v>
+        <v>0.326</v>
       </c>
       <c r="G39" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="K39" t="n">
         <v>0.003</v>
       </c>
-      <c r="H39" t="n">
-        <v>0.181</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0.002</v>
-      </c>
       <c r="L39" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="40">
@@ -5108,31 +5108,31 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>2.812</v>
+        <v>2.875</v>
       </c>
       <c r="F40" t="n">
-        <v>0.269</v>
+        <v>0.325</v>
       </c>
       <c r="G40" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="H40" t="n">
-        <v>0.168</v>
+        <v>0.224</v>
       </c>
       <c r="I40" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.054</v>
+        <v>0.062</v>
       </c>
       <c r="K40" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="L40" t="n">
-        <v>0.041</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="41">
@@ -5150,30 +5150,198 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.036</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.719</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.033</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.042</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.812</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.041</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="n">
         <v>2.823</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F45" t="n">
         <v>0.264</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G45" t="n">
         <v>0.006</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H45" t="n">
         <v>0.154</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I45" t="n">
         <v>0.001</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J45" t="n">
         <v>0.056</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K45" t="n">
         <v>0.004</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L45" t="n">
         <v>0.043</v>
       </c>
     </row>
@@ -5512,13 +5680,13 @@
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
         <v>3.427</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.948</v>
       </c>
     </row>
     <row r="11">
@@ -5544,13 +5712,13 @@
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
         <v>0.209</v>
       </c>
       <c r="H11" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="12">
@@ -5576,13 +5744,13 @@
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
         <v>0.006</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.002</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="13">
@@ -5608,13 +5776,13 @@
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
         <v>0.121</v>
       </c>
       <c r="H13" t="n">
-        <v>0.062</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="14">
@@ -5640,7 +5808,7 @@
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
         <v>0.002</v>
@@ -5672,13 +5840,13 @@
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
         <v>0.045</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="16">
@@ -5704,13 +5872,13 @@
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
         <v>0.01</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.007</v>
+        <v>-0.008999999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -5736,13 +5904,13 @@
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
         <v>0.026</v>
       </c>
       <c r="H17" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="18">
@@ -6536,13 +6704,13 @@
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G42" t="n">
         <v>3.427</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.6879999999999999</v>
+        <v>-0.948</v>
       </c>
     </row>
     <row r="43">
@@ -6568,13 +6736,13 @@
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G43" t="n">
         <v>0.209</v>
       </c>
       <c r="H43" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="44">
@@ -6600,13 +6768,13 @@
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G44" t="n">
         <v>0.006</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.002</v>
+        <v>-0.006</v>
       </c>
     </row>
     <row r="45">
@@ -6632,13 +6800,13 @@
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G45" t="n">
         <v>0.121</v>
       </c>
       <c r="H45" t="n">
-        <v>0.062</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="46">
@@ -6664,7 +6832,7 @@
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G46" t="n">
         <v>0.002</v>
@@ -6696,13 +6864,13 @@
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G47" t="n">
         <v>0.045</v>
       </c>
       <c r="H47" t="n">
-        <v>0.001</v>
+        <v>-0.005</v>
       </c>
     </row>
     <row r="48">
@@ -6728,13 +6896,13 @@
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G48" t="n">
         <v>0.01</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.007</v>
+        <v>-0.008999999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -6760,13 +6928,13 @@
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G49" t="n">
         <v>0.026</v>
       </c>
       <c r="H49" t="n">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="50">
@@ -7940,13 +8108,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
         <v>3.042</v>
       </c>
       <c r="H19" t="n">
-        <v>0.781</v>
+        <v>1.021</v>
       </c>
     </row>
     <row r="20">
@@ -7974,13 +8142,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
         <v>2.604</v>
       </c>
       <c r="H20" t="n">
-        <v>1.25</v>
+        <v>1.813</v>
       </c>
     </row>
     <row r="21">
@@ -8008,13 +8176,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
         <v>2.167</v>
       </c>
       <c r="H21" t="n">
-        <v>0.927</v>
+        <v>1.427</v>
       </c>
     </row>
     <row r="22">
@@ -8042,13 +8210,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
         <v>3.156</v>
       </c>
       <c r="H22" t="n">
-        <v>1.177</v>
+        <v>1.469</v>
       </c>
     </row>
     <row r="23">
@@ -8076,13 +8244,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
         <v>3.177</v>
       </c>
       <c r="H23" t="n">
-        <v>1.104</v>
+        <v>1.427</v>
       </c>
     </row>
     <row r="24">
@@ -8110,13 +8278,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
         <v>2.688</v>
       </c>
       <c r="H24" t="n">
-        <v>1.438</v>
+        <v>1.812</v>
       </c>
     </row>
     <row r="25">
@@ -8144,13 +8312,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
         <v>3.417</v>
       </c>
       <c r="H25" t="n">
-        <v>1.146</v>
+        <v>1.427</v>
       </c>
     </row>
     <row r="26">
@@ -8178,13 +8346,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
         <v>3.406</v>
       </c>
       <c r="H26" t="n">
-        <v>1.219</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="27">
@@ -8212,13 +8380,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
         <v>2.677</v>
       </c>
       <c r="H27" t="n">
-        <v>1.365</v>
+        <v>1.792</v>
       </c>
     </row>
     <row r="28">
@@ -8246,13 +8414,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
         <v>2.302</v>
       </c>
       <c r="H28" t="n">
-        <v>1.042</v>
+        <v>1.469</v>
       </c>
     </row>
     <row r="29">
@@ -8280,13 +8448,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G29" t="n">
         <v>3.417</v>
       </c>
       <c r="H29" t="n">
-        <v>1.24</v>
+        <v>1.479</v>
       </c>
     </row>
     <row r="30">
@@ -8314,13 +8482,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
         <v>3.406</v>
       </c>
       <c r="H30" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="31">
@@ -8348,13 +8516,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G31" t="n">
         <v>2.979</v>
       </c>
       <c r="H31" t="n">
-        <v>1.323</v>
+        <v>1.583</v>
       </c>
     </row>
     <row r="32">
@@ -8382,13 +8550,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
         <v>3.385</v>
       </c>
       <c r="H32" t="n">
-        <v>1.396</v>
+        <v>1.552</v>
       </c>
     </row>
     <row r="33">
@@ -8416,13 +8584,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G33" t="n">
         <v>3.26</v>
       </c>
       <c r="H33" t="n">
-        <v>1.448</v>
+        <v>1.635</v>
       </c>
     </row>
     <row r="34">
@@ -8450,13 +8618,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G34" t="n">
         <v>3.135</v>
       </c>
       <c r="H34" t="n">
-        <v>1.469</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="35">
@@ -8484,13 +8652,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G35" t="n">
         <v>3.052</v>
       </c>
       <c r="H35" t="n">
-        <v>1.542</v>
+        <v>1.781</v>
       </c>
     </row>
     <row r="36">
@@ -10252,13 +10420,13 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G87" t="n">
         <v>3.042</v>
       </c>
       <c r="H87" t="n">
-        <v>0.781</v>
+        <v>1.021</v>
       </c>
     </row>
     <row r="88">
@@ -10286,13 +10454,13 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G88" t="n">
         <v>2.604</v>
       </c>
       <c r="H88" t="n">
-        <v>1.25</v>
+        <v>1.813</v>
       </c>
     </row>
     <row r="89">
@@ -10320,13 +10488,13 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G89" t="n">
         <v>2.167</v>
       </c>
       <c r="H89" t="n">
-        <v>0.927</v>
+        <v>1.427</v>
       </c>
     </row>
     <row r="90">
@@ -10354,13 +10522,13 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G90" t="n">
         <v>3.156</v>
       </c>
       <c r="H90" t="n">
-        <v>1.177</v>
+        <v>1.469</v>
       </c>
     </row>
     <row r="91">
@@ -10388,13 +10556,13 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G91" t="n">
         <v>3.177</v>
       </c>
       <c r="H91" t="n">
-        <v>1.104</v>
+        <v>1.427</v>
       </c>
     </row>
     <row r="92">
@@ -10422,13 +10590,13 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G92" t="n">
         <v>2.688</v>
       </c>
       <c r="H92" t="n">
-        <v>1.438</v>
+        <v>1.812</v>
       </c>
     </row>
     <row r="93">
@@ -10456,13 +10624,13 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G93" t="n">
         <v>3.417</v>
       </c>
       <c r="H93" t="n">
-        <v>1.146</v>
+        <v>1.427</v>
       </c>
     </row>
     <row r="94">
@@ -10490,13 +10658,13 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G94" t="n">
         <v>3.406</v>
       </c>
       <c r="H94" t="n">
-        <v>1.219</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="95">
@@ -10524,13 +10692,13 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G95" t="n">
         <v>2.677</v>
       </c>
       <c r="H95" t="n">
-        <v>1.365</v>
+        <v>1.792</v>
       </c>
     </row>
     <row r="96">
@@ -10558,13 +10726,13 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G96" t="n">
         <v>2.302</v>
       </c>
       <c r="H96" t="n">
-        <v>1.042</v>
+        <v>1.469</v>
       </c>
     </row>
     <row r="97">
@@ -10592,13 +10760,13 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G97" t="n">
         <v>3.417</v>
       </c>
       <c r="H97" t="n">
-        <v>1.24</v>
+        <v>1.479</v>
       </c>
     </row>
     <row r="98">
@@ -10626,13 +10794,13 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G98" t="n">
         <v>3.406</v>
       </c>
       <c r="H98" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="99">
@@ -10660,13 +10828,13 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G99" t="n">
         <v>2.979</v>
       </c>
       <c r="H99" t="n">
-        <v>1.323</v>
+        <v>1.583</v>
       </c>
     </row>
     <row r="100">
@@ -10694,13 +10862,13 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G100" t="n">
         <v>3.385</v>
       </c>
       <c r="H100" t="n">
-        <v>1.396</v>
+        <v>1.552</v>
       </c>
     </row>
     <row r="101">
@@ -10728,13 +10896,13 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G101" t="n">
         <v>3.26</v>
       </c>
       <c r="H101" t="n">
-        <v>1.448</v>
+        <v>1.635</v>
       </c>
     </row>
     <row r="102">
@@ -10762,13 +10930,13 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G102" t="n">
         <v>3.135</v>
       </c>
       <c r="H102" t="n">
-        <v>1.469</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="103">
@@ -10796,13 +10964,13 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G103" t="n">
         <v>3.052</v>
       </c>
       <c r="H103" t="n">
-        <v>1.542</v>
+        <v>1.781</v>
       </c>
     </row>
     <row r="104">
@@ -12385,13 +12553,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
         <v>2.604</v>
       </c>
       <c r="H14" t="n">
-        <v>0.49</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="15">
@@ -12414,13 +12582,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
         <v>2.76</v>
       </c>
       <c r="H15" t="n">
-        <v>0.802</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="16">
@@ -12443,13 +12611,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
         <v>3.115</v>
       </c>
       <c r="H16" t="n">
-        <v>0.49</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="17">
@@ -12472,13 +12640,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
         <v>2.531</v>
       </c>
       <c r="H17" t="n">
-        <v>0.469</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="18">
@@ -12501,13 +12669,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
         <v>3.354</v>
       </c>
       <c r="H18" t="n">
-        <v>0.583</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="19">
@@ -12530,13 +12698,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
         <v>2.521</v>
       </c>
       <c r="H19" t="n">
-        <v>0.49</v>
+        <v>0.646</v>
       </c>
     </row>
     <row r="20">
@@ -12559,13 +12727,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
         <v>3.01</v>
       </c>
       <c r="H20" t="n">
-        <v>0.667</v>
+        <v>0.906</v>
       </c>
     </row>
     <row r="21">
@@ -12588,13 +12756,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
         <v>2.75</v>
       </c>
       <c r="H21" t="n">
-        <v>0.854</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="22">
@@ -12617,13 +12785,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
         <v>3.354</v>
       </c>
       <c r="H22" t="n">
-        <v>0.646</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="23">
@@ -12646,13 +12814,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
         <v>2.865</v>
       </c>
       <c r="H23" t="n">
-        <v>0.927</v>
+        <v>1.062</v>
       </c>
     </row>
     <row r="24">
@@ -12675,13 +12843,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
         <v>2.719</v>
       </c>
       <c r="H24" t="n">
-        <v>0.896</v>
+        <v>1.167</v>
       </c>
     </row>
     <row r="25">
@@ -12704,13 +12872,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
         <v>2.698</v>
       </c>
       <c r="H25" t="n">
-        <v>0.917</v>
+        <v>1.229</v>
       </c>
     </row>
     <row r="26">
@@ -13777,13 +13945,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G62" t="n">
         <v>2.604</v>
       </c>
       <c r="H62" t="n">
-        <v>0.49</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="63">
@@ -13806,13 +13974,13 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G63" t="n">
         <v>2.76</v>
       </c>
       <c r="H63" t="n">
-        <v>0.802</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="64">
@@ -13835,13 +14003,13 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G64" t="n">
         <v>3.115</v>
       </c>
       <c r="H64" t="n">
-        <v>0.49</v>
+        <v>0.635</v>
       </c>
     </row>
     <row r="65">
@@ -13864,13 +14032,13 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G65" t="n">
         <v>2.531</v>
       </c>
       <c r="H65" t="n">
-        <v>0.469</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="66">
@@ -13893,13 +14061,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G66" t="n">
         <v>3.354</v>
       </c>
       <c r="H66" t="n">
-        <v>0.583</v>
+        <v>0.677</v>
       </c>
     </row>
     <row r="67">
@@ -13922,13 +14090,13 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G67" t="n">
         <v>2.521</v>
       </c>
       <c r="H67" t="n">
-        <v>0.49</v>
+        <v>0.646</v>
       </c>
     </row>
     <row r="68">
@@ -13951,13 +14119,13 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G68" t="n">
         <v>3.01</v>
       </c>
       <c r="H68" t="n">
-        <v>0.667</v>
+        <v>0.906</v>
       </c>
     </row>
     <row r="69">
@@ -13980,13 +14148,13 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G69" t="n">
         <v>2.75</v>
       </c>
       <c r="H69" t="n">
-        <v>0.854</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="70">
@@ -14009,13 +14177,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G70" t="n">
         <v>3.354</v>
       </c>
       <c r="H70" t="n">
-        <v>0.646</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="71">
@@ -14038,13 +14206,13 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G71" t="n">
         <v>2.865</v>
       </c>
       <c r="H71" t="n">
-        <v>0.927</v>
+        <v>1.062</v>
       </c>
     </row>
     <row r="72">
@@ -14067,13 +14235,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G72" t="n">
         <v>2.719</v>
       </c>
       <c r="H72" t="n">
-        <v>0.896</v>
+        <v>1.167</v>
       </c>
     </row>
     <row r="73">
@@ -14096,13 +14264,13 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G73" t="n">
         <v>2.698</v>
       </c>
       <c r="H73" t="n">
-        <v>0.917</v>
+        <v>1.229</v>
       </c>
     </row>
     <row r="74">
@@ -15109,13 +15277,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
         <v>2.427</v>
       </c>
       <c r="H10" t="n">
-        <v>0.333</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="11">
@@ -15138,13 +15306,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
         <v>2.312</v>
       </c>
       <c r="H11" t="n">
-        <v>0.396</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="12">
@@ -15167,13 +15335,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
         <v>2.25</v>
       </c>
       <c r="H12" t="n">
-        <v>0.448</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="13">
@@ -15196,13 +15364,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
         <v>2.354</v>
       </c>
       <c r="H13" t="n">
-        <v>0.646</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="14">
@@ -15225,13 +15393,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
         <v>2.354</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.781</v>
       </c>
     </row>
     <row r="15">
@@ -15254,13 +15422,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
         <v>2.406</v>
       </c>
       <c r="H15" t="n">
-        <v>0.646</v>
+        <v>0.781</v>
       </c>
     </row>
     <row r="16">
@@ -15283,13 +15451,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
         <v>2.344</v>
       </c>
       <c r="H16" t="n">
-        <v>0.74</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="17">
@@ -15312,13 +15480,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
         <v>2.396</v>
       </c>
       <c r="H17" t="n">
-        <v>0.74</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="18">
@@ -16037,13 +16205,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G42" t="n">
         <v>2.427</v>
       </c>
       <c r="H42" t="n">
-        <v>0.333</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="43">
@@ -16066,13 +16234,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G43" t="n">
         <v>2.312</v>
       </c>
       <c r="H43" t="n">
-        <v>0.396</v>
+        <v>0.583</v>
       </c>
     </row>
     <row r="44">
@@ -16095,13 +16263,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G44" t="n">
         <v>2.25</v>
       </c>
       <c r="H44" t="n">
-        <v>0.448</v>
+        <v>0.604</v>
       </c>
     </row>
     <row r="45">
@@ -16124,13 +16292,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G45" t="n">
         <v>2.354</v>
       </c>
       <c r="H45" t="n">
-        <v>0.646</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="46">
@@ -16153,13 +16321,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G46" t="n">
         <v>2.354</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.781</v>
       </c>
     </row>
     <row r="47">
@@ -16182,13 +16350,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G47" t="n">
         <v>2.406</v>
       </c>
       <c r="H47" t="n">
-        <v>0.646</v>
+        <v>0.781</v>
       </c>
     </row>
     <row r="48">
@@ -16211,13 +16379,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G48" t="n">
         <v>2.344</v>
       </c>
       <c r="H48" t="n">
-        <v>0.74</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="49">
@@ -16240,13 +16408,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G49" t="n">
         <v>2.396</v>
       </c>
       <c r="H49" t="n">
-        <v>0.74</v>
+        <v>0.865</v>
       </c>
     </row>
     <row r="50">
@@ -16963,13 +17131,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
         <v>2.729</v>
       </c>
       <c r="H8" t="n">
-        <v>0.74</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="9">
@@ -16992,13 +17160,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G9" t="n">
         <v>2.438</v>
       </c>
       <c r="H9" t="n">
-        <v>0.708</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="10">
@@ -17021,13 +17189,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
         <v>2.74</v>
       </c>
       <c r="H10" t="n">
-        <v>1.104</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="11">
@@ -17050,13 +17218,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G11" t="n">
         <v>3.021</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="12">
@@ -17079,13 +17247,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
         <v>2.948</v>
       </c>
       <c r="H12" t="n">
-        <v>1.094</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="13">
@@ -17108,13 +17276,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
         <v>3.021</v>
       </c>
       <c r="H13" t="n">
-        <v>0.865</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="14">
@@ -17659,13 +17827,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
         <v>2.729</v>
       </c>
       <c r="H32" t="n">
-        <v>0.74</v>
+        <v>0.823</v>
       </c>
     </row>
     <row r="33">
@@ -17688,13 +17856,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G33" t="n">
         <v>2.438</v>
       </c>
       <c r="H33" t="n">
-        <v>0.708</v>
+        <v>0.927</v>
       </c>
     </row>
     <row r="34">
@@ -17717,13 +17885,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G34" t="n">
         <v>2.74</v>
       </c>
       <c r="H34" t="n">
-        <v>1.104</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="35">
@@ -17746,13 +17914,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G35" t="n">
         <v>3.021</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.833</v>
       </c>
     </row>
     <row r="36">
@@ -17775,13 +17943,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G36" t="n">
         <v>2.948</v>
       </c>
       <c r="H36" t="n">
-        <v>1.094</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="37">
@@ -17804,13 +17972,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G37" t="n">
         <v>3.021</v>
       </c>
       <c r="H37" t="n">
-        <v>0.865</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="38">
@@ -18172,7 +18340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T41"/>
+  <dimension ref="A1:T45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19468,265 +19636,265 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>2.823</v>
+        <v>4.01</v>
       </c>
       <c r="F20" t="n">
-        <v>3.021</v>
+        <v>3.927</v>
       </c>
       <c r="G20" t="n">
-        <v>3.24</v>
+        <v>4.594</v>
       </c>
       <c r="H20" t="n">
-        <v>3.448</v>
+        <v>4.604</v>
       </c>
       <c r="I20" t="n">
-        <v>0.485</v>
+        <v>0.379</v>
       </c>
       <c r="J20" t="n">
-        <v>0.175</v>
+        <v>0.174</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.115</v>
       </c>
       <c r="L20" t="n">
-        <v>0.025</v>
+        <v>0.039</v>
       </c>
       <c r="M20" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.161</v>
       </c>
       <c r="N20" t="n">
-        <v>0.127</v>
+        <v>0.169</v>
       </c>
       <c r="O20" t="n">
-        <v>0.054</v>
+        <v>0.032</v>
       </c>
       <c r="P20" t="n">
-        <v>0.61</v>
+        <v>0.843</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.311</v>
+        <v>0.362</v>
       </c>
       <c r="R20" t="n">
-        <v>0.774</v>
+        <v>0.651</v>
       </c>
       <c r="S20" t="n">
-        <v>2.922</v>
+        <v>3.969</v>
       </c>
       <c r="T20" t="n">
-        <v>3.344</v>
+        <v>4.599</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>2.979</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>3.219</v>
+        <v>3.99</v>
       </c>
       <c r="G21" t="n">
-        <v>3.458</v>
+        <v>4.615</v>
       </c>
       <c r="H21" t="n">
-        <v>3.698</v>
+        <v>4.646</v>
       </c>
       <c r="I21" t="n">
-        <v>0.48</v>
+        <v>0.369</v>
       </c>
       <c r="J21" t="n">
-        <v>0.179</v>
+        <v>0.199</v>
       </c>
       <c r="K21" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.132</v>
       </c>
       <c r="L21" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.025</v>
       </c>
-      <c r="M21" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.037</v>
-      </c>
       <c r="P21" t="n">
-        <v>0.612</v>
+        <v>0.99</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.302</v>
+        <v>0.385</v>
       </c>
       <c r="R21" t="n">
-        <v>0.749</v>
+        <v>0.721</v>
       </c>
       <c r="S21" t="n">
-        <v>3.099</v>
+        <v>3.995</v>
       </c>
       <c r="T21" t="n">
-        <v>3.578</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>3.146</v>
+        <v>4.333</v>
       </c>
       <c r="F22" t="n">
-        <v>3.333</v>
+        <v>4.219</v>
       </c>
       <c r="G22" t="n">
-        <v>3.677</v>
+        <v>4.75</v>
       </c>
       <c r="H22" t="n">
-        <v>3.833</v>
+        <v>4.781</v>
       </c>
       <c r="I22" t="n">
-        <v>0.451</v>
+        <v>0.344</v>
       </c>
       <c r="J22" t="n">
-        <v>0.178</v>
+        <v>0.209</v>
       </c>
       <c r="K22" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="L22" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="O22" t="n">
         <v>0.03</v>
       </c>
-      <c r="M22" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.168</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.046</v>
-      </c>
       <c r="P22" t="n">
-        <v>0.764</v>
+        <v>1.172</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.291</v>
+        <v>0.415</v>
       </c>
       <c r="R22" t="n">
-        <v>0.708</v>
+        <v>0.721</v>
       </c>
       <c r="S22" t="n">
-        <v>3.24</v>
+        <v>4.276</v>
       </c>
       <c r="T22" t="n">
-        <v>3.755</v>
+        <v>4.766</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>3.365</v>
+        <v>4.312</v>
       </c>
       <c r="F23" t="n">
-        <v>3.573</v>
+        <v>4.26</v>
       </c>
       <c r="G23" t="n">
-        <v>3.927</v>
+        <v>4.792</v>
       </c>
       <c r="H23" t="n">
-        <v>4.01</v>
+        <v>4.781</v>
       </c>
       <c r="I23" t="n">
-        <v>0.48</v>
+        <v>0.341</v>
       </c>
       <c r="J23" t="n">
-        <v>0.171</v>
+        <v>0.202</v>
       </c>
       <c r="K23" t="n">
-        <v>0.089</v>
+        <v>0.147</v>
       </c>
       <c r="L23" t="n">
-        <v>0.031</v>
+        <v>0.029</v>
       </c>
       <c r="M23" t="n">
-        <v>0.128</v>
+        <v>0.151</v>
       </c>
       <c r="N23" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="O23" t="n">
-        <v>0.027</v>
+        <v>0.014</v>
       </c>
       <c r="P23" t="n">
-        <v>0.673</v>
+        <v>1.114</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.318</v>
+        <v>0.41</v>
       </c>
       <c r="R23" t="n">
-        <v>0.675</v>
+        <v>0.707</v>
       </c>
       <c r="S23" t="n">
-        <v>3.469</v>
+        <v>4.286</v>
       </c>
       <c r="T23" t="n">
-        <v>3.969</v>
+        <v>4.786</v>
       </c>
     </row>
     <row r="24">
@@ -19744,55 +19912,55 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>3.552</v>
+        <v>2.823</v>
       </c>
       <c r="F24" t="n">
-        <v>3.708</v>
+        <v>3.021</v>
       </c>
       <c r="G24" t="n">
-        <v>4.24</v>
+        <v>3.24</v>
       </c>
       <c r="H24" t="n">
-        <v>4.198</v>
+        <v>3.448</v>
       </c>
       <c r="I24" t="n">
-        <v>0.451</v>
+        <v>0.485</v>
       </c>
       <c r="J24" t="n">
-        <v>0.152</v>
+        <v>0.175</v>
       </c>
       <c r="K24" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="M24" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="L24" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.136</v>
-      </c>
       <c r="N24" t="n">
-        <v>0.179</v>
+        <v>0.127</v>
       </c>
       <c r="O24" t="n">
-        <v>0.035</v>
+        <v>0.054</v>
       </c>
       <c r="P24" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.343</v>
+        <v>0.311</v>
       </c>
       <c r="R24" t="n">
-        <v>0.644</v>
+        <v>0.774</v>
       </c>
       <c r="S24" t="n">
-        <v>3.63</v>
+        <v>2.922</v>
       </c>
       <c r="T24" t="n">
-        <v>4.219</v>
+        <v>3.344</v>
       </c>
     </row>
     <row r="25">
@@ -19810,55 +19978,55 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>3.562</v>
+        <v>2.979</v>
       </c>
       <c r="F25" t="n">
-        <v>3.74</v>
+        <v>3.219</v>
       </c>
       <c r="G25" t="n">
-        <v>4.281</v>
+        <v>3.458</v>
       </c>
       <c r="H25" t="n">
-        <v>4.26</v>
+        <v>3.698</v>
       </c>
       <c r="I25" t="n">
-        <v>0.446</v>
+        <v>0.48</v>
       </c>
       <c r="J25" t="n">
-        <v>0.153</v>
+        <v>0.179</v>
       </c>
       <c r="K25" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L25" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="O25" t="n">
         <v>0.037</v>
       </c>
-      <c r="M25" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.029</v>
-      </c>
       <c r="P25" t="n">
-        <v>0.607</v>
+        <v>0.612</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.32</v>
+        <v>0.302</v>
       </c>
       <c r="R25" t="n">
-        <v>0.622</v>
+        <v>0.749</v>
       </c>
       <c r="S25" t="n">
-        <v>3.651</v>
+        <v>3.099</v>
       </c>
       <c r="T25" t="n">
-        <v>4.271</v>
+        <v>3.578</v>
       </c>
     </row>
     <row r="26">
@@ -19876,55 +20044,55 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>3.729</v>
+        <v>3.146</v>
       </c>
       <c r="F26" t="n">
-        <v>3.781</v>
+        <v>3.333</v>
       </c>
       <c r="G26" t="n">
-        <v>4.427</v>
+        <v>3.677</v>
       </c>
       <c r="H26" t="n">
-        <v>4.427</v>
+        <v>3.833</v>
       </c>
       <c r="I26" t="n">
-        <v>0.498</v>
+        <v>0.451</v>
       </c>
       <c r="J26" t="n">
-        <v>0.159</v>
+        <v>0.178</v>
       </c>
       <c r="K26" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>0.065</v>
+        <v>0.03</v>
       </c>
       <c r="M26" t="n">
-        <v>0.149</v>
+        <v>0.112</v>
       </c>
       <c r="N26" t="n">
-        <v>0.209</v>
+        <v>0.168</v>
       </c>
       <c r="O26" t="n">
-        <v>0.053</v>
+        <v>0.046</v>
       </c>
       <c r="P26" t="n">
-        <v>0.652</v>
+        <v>0.764</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.324</v>
+        <v>0.291</v>
       </c>
       <c r="R26" t="n">
-        <v>0.645</v>
+        <v>0.708</v>
       </c>
       <c r="S26" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T26" t="n">
         <v>3.755</v>
-      </c>
-      <c r="T26" t="n">
-        <v>4.427</v>
       </c>
     </row>
     <row r="27">
@@ -19942,55 +20110,55 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>3.688</v>
+        <v>3.365</v>
       </c>
       <c r="F27" t="n">
-        <v>3.76</v>
+        <v>3.573</v>
       </c>
       <c r="G27" t="n">
-        <v>4.427</v>
+        <v>3.927</v>
       </c>
       <c r="H27" t="n">
-        <v>4.396</v>
+        <v>4.01</v>
       </c>
       <c r="I27" t="n">
-        <v>0.442</v>
+        <v>0.48</v>
       </c>
       <c r="J27" t="n">
-        <v>0.141</v>
+        <v>0.171</v>
       </c>
       <c r="K27" t="n">
-        <v>0.08</v>
+        <v>0.089</v>
       </c>
       <c r="L27" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.031</v>
       </c>
       <c r="M27" t="n">
-        <v>0.144</v>
+        <v>0.128</v>
       </c>
       <c r="N27" t="n">
-        <v>0.205</v>
+        <v>0.17</v>
       </c>
       <c r="O27" t="n">
-        <v>0.058</v>
+        <v>0.027</v>
       </c>
       <c r="P27" t="n">
-        <v>0.606</v>
+        <v>0.673</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.339</v>
+        <v>0.318</v>
       </c>
       <c r="R27" t="n">
-        <v>0.639</v>
+        <v>0.675</v>
       </c>
       <c r="S27" t="n">
-        <v>3.724</v>
+        <v>3.469</v>
       </c>
       <c r="T27" t="n">
-        <v>4.411</v>
+        <v>3.969</v>
       </c>
     </row>
     <row r="28">
@@ -20008,55 +20176,55 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>3.802</v>
+        <v>3.552</v>
       </c>
       <c r="F28" t="n">
-        <v>3.844</v>
+        <v>3.708</v>
       </c>
       <c r="G28" t="n">
-        <v>4.51</v>
+        <v>4.24</v>
       </c>
       <c r="H28" t="n">
-        <v>4.531</v>
+        <v>4.198</v>
       </c>
       <c r="I28" t="n">
-        <v>0.406</v>
+        <v>0.451</v>
       </c>
       <c r="J28" t="n">
-        <v>0.174</v>
+        <v>0.152</v>
       </c>
       <c r="K28" t="n">
-        <v>0.106</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>0.091</v>
+        <v>0.041</v>
       </c>
       <c r="M28" t="n">
-        <v>0.149</v>
+        <v>0.136</v>
       </c>
       <c r="N28" t="n">
-        <v>0.214</v>
+        <v>0.179</v>
       </c>
       <c r="O28" t="n">
-        <v>0.073</v>
+        <v>0.035</v>
       </c>
       <c r="P28" t="n">
-        <v>0.798</v>
+        <v>0.65</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.324</v>
+        <v>0.343</v>
       </c>
       <c r="R28" t="n">
-        <v>0.68</v>
+        <v>0.644</v>
       </c>
       <c r="S28" t="n">
-        <v>3.823</v>
+        <v>3.63</v>
       </c>
       <c r="T28" t="n">
-        <v>4.521</v>
+        <v>4.219</v>
       </c>
     </row>
     <row r="29">
@@ -20074,55 +20242,55 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>3.896</v>
+        <v>3.562</v>
       </c>
       <c r="F29" t="n">
-        <v>3.927</v>
+        <v>3.74</v>
       </c>
       <c r="G29" t="n">
-        <v>4.573</v>
+        <v>4.281</v>
       </c>
       <c r="H29" t="n">
-        <v>4.573</v>
+        <v>4.26</v>
       </c>
       <c r="I29" t="n">
-        <v>0.394</v>
+        <v>0.446</v>
       </c>
       <c r="J29" t="n">
         <v>0.153</v>
       </c>
       <c r="K29" t="n">
-        <v>0.097</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>0.131</v>
+        <v>0.037</v>
       </c>
       <c r="M29" t="n">
-        <v>0.163</v>
+        <v>0.148</v>
       </c>
       <c r="N29" t="n">
-        <v>0.22</v>
+        <v>0.198</v>
       </c>
       <c r="O29" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.029</v>
       </c>
       <c r="P29" t="n">
-        <v>0.727</v>
+        <v>0.607</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.331</v>
+        <v>0.32</v>
       </c>
       <c r="R29" t="n">
-        <v>0.677</v>
+        <v>0.622</v>
       </c>
       <c r="S29" t="n">
-        <v>3.911</v>
+        <v>3.651</v>
       </c>
       <c r="T29" t="n">
-        <v>4.573</v>
+        <v>4.271</v>
       </c>
     </row>
     <row r="30">
@@ -20140,61 +20308,61 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>3.979</v>
+        <v>3.729</v>
       </c>
       <c r="F30" t="n">
-        <v>3.885</v>
+        <v>3.781</v>
       </c>
       <c r="G30" t="n">
-        <v>4.615</v>
+        <v>4.427</v>
       </c>
       <c r="H30" t="n">
-        <v>4.615</v>
+        <v>4.427</v>
       </c>
       <c r="I30" t="n">
-        <v>0.405</v>
+        <v>0.498</v>
       </c>
       <c r="J30" t="n">
-        <v>0.153</v>
+        <v>0.159</v>
       </c>
       <c r="K30" t="n">
-        <v>0.105</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>0.142</v>
+        <v>0.065</v>
       </c>
       <c r="M30" t="n">
-        <v>0.15</v>
+        <v>0.149</v>
       </c>
       <c r="N30" t="n">
-        <v>0.226</v>
+        <v>0.209</v>
       </c>
       <c r="O30" t="n">
-        <v>0.074</v>
+        <v>0.053</v>
       </c>
       <c r="P30" t="n">
-        <v>0.75</v>
+        <v>0.652</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.364</v>
+        <v>0.324</v>
       </c>
       <c r="R30" t="n">
-        <v>0.7</v>
+        <v>0.645</v>
       </c>
       <c r="S30" t="n">
-        <v>3.932</v>
+        <v>3.755</v>
       </c>
       <c r="T30" t="n">
-        <v>4.615</v>
+        <v>4.427</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -20203,64 +20371,64 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>2.812</v>
+        <v>3.688</v>
       </c>
       <c r="F31" t="n">
-        <v>3.094</v>
+        <v>3.76</v>
       </c>
       <c r="G31" t="n">
-        <v>3.24</v>
+        <v>4.427</v>
       </c>
       <c r="H31" t="n">
-        <v>3.448</v>
+        <v>4.396</v>
       </c>
       <c r="I31" t="n">
-        <v>0.476</v>
+        <v>0.442</v>
       </c>
       <c r="J31" t="n">
-        <v>0.175</v>
+        <v>0.141</v>
       </c>
       <c r="K31" t="n">
-        <v>0.078</v>
+        <v>0.08</v>
       </c>
       <c r="L31" t="n">
-        <v>0.029</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>0.091</v>
+        <v>0.144</v>
       </c>
       <c r="N31" t="n">
-        <v>0.133</v>
+        <v>0.205</v>
       </c>
       <c r="O31" t="n">
-        <v>0.049</v>
+        <v>0.058</v>
       </c>
       <c r="P31" t="n">
-        <v>0.728</v>
+        <v>0.606</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.294</v>
+        <v>0.339</v>
       </c>
       <c r="R31" t="n">
-        <v>0.753</v>
+        <v>0.639</v>
       </c>
       <c r="S31" t="n">
-        <v>2.953</v>
+        <v>3.724</v>
       </c>
       <c r="T31" t="n">
-        <v>3.344</v>
+        <v>4.411</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -20269,64 +20437,64 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>2.844</v>
+        <v>3.802</v>
       </c>
       <c r="F32" t="n">
-        <v>3.177</v>
+        <v>3.844</v>
       </c>
       <c r="G32" t="n">
-        <v>3.312</v>
+        <v>4.51</v>
       </c>
       <c r="H32" t="n">
-        <v>3.51</v>
+        <v>4.531</v>
       </c>
       <c r="I32" t="n">
-        <v>0.486</v>
+        <v>0.406</v>
       </c>
       <c r="J32" t="n">
-        <v>0.179</v>
+        <v>0.174</v>
       </c>
       <c r="K32" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="L32" t="n">
-        <v>0.023</v>
+        <v>0.091</v>
       </c>
       <c r="M32" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="N32" t="n">
-        <v>0.134</v>
+        <v>0.214</v>
       </c>
       <c r="O32" t="n">
-        <v>0.04</v>
+        <v>0.073</v>
       </c>
       <c r="P32" t="n">
-        <v>0.626</v>
+        <v>0.798</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.306</v>
+        <v>0.324</v>
       </c>
       <c r="R32" t="n">
-        <v>0.755</v>
+        <v>0.68</v>
       </c>
       <c r="S32" t="n">
-        <v>3.01</v>
+        <v>3.823</v>
       </c>
       <c r="T32" t="n">
-        <v>3.411</v>
+        <v>4.521</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -20335,64 +20503,64 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>3.042</v>
+        <v>3.896</v>
       </c>
       <c r="F33" t="n">
-        <v>3.219</v>
+        <v>3.927</v>
       </c>
       <c r="G33" t="n">
-        <v>3.573</v>
+        <v>4.573</v>
       </c>
       <c r="H33" t="n">
-        <v>3.74</v>
+        <v>4.573</v>
       </c>
       <c r="I33" t="n">
-        <v>0.423</v>
+        <v>0.394</v>
       </c>
       <c r="J33" t="n">
-        <v>0.184</v>
+        <v>0.153</v>
       </c>
       <c r="K33" t="n">
         <v>0.097</v>
       </c>
       <c r="L33" t="n">
-        <v>0.031</v>
+        <v>0.131</v>
       </c>
       <c r="M33" t="n">
-        <v>0.118</v>
+        <v>0.163</v>
       </c>
       <c r="N33" t="n">
-        <v>0.152</v>
+        <v>0.22</v>
       </c>
       <c r="O33" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P33" t="n">
-        <v>0.764</v>
+        <v>0.727</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.342</v>
+        <v>0.331</v>
       </c>
       <c r="R33" t="n">
-        <v>0.72</v>
+        <v>0.677</v>
       </c>
       <c r="S33" t="n">
-        <v>3.13</v>
+        <v>3.911</v>
       </c>
       <c r="T33" t="n">
-        <v>3.656</v>
+        <v>4.573</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -20401,58 +20569,58 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>3.25</v>
+        <v>3.979</v>
       </c>
       <c r="F34" t="n">
-        <v>3.469</v>
+        <v>3.885</v>
       </c>
       <c r="G34" t="n">
-        <v>3.792</v>
+        <v>4.615</v>
       </c>
       <c r="H34" t="n">
-        <v>3.938</v>
+        <v>4.615</v>
       </c>
       <c r="I34" t="n">
-        <v>0.454</v>
+        <v>0.405</v>
       </c>
       <c r="J34" t="n">
-        <v>0.161</v>
+        <v>0.153</v>
       </c>
       <c r="K34" t="n">
-        <v>0.092</v>
+        <v>0.105</v>
       </c>
       <c r="L34" t="n">
-        <v>0.026</v>
+        <v>0.142</v>
       </c>
       <c r="M34" t="n">
-        <v>0.123</v>
+        <v>0.15</v>
       </c>
       <c r="N34" t="n">
-        <v>0.16</v>
+        <v>0.226</v>
       </c>
       <c r="O34" t="n">
-        <v>0.034</v>
+        <v>0.074</v>
       </c>
       <c r="P34" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.321</v>
+        <v>0.364</v>
       </c>
       <c r="R34" t="n">
-        <v>0.678</v>
+        <v>0.7</v>
       </c>
       <c r="S34" t="n">
-        <v>3.359</v>
+        <v>3.932</v>
       </c>
       <c r="T34" t="n">
-        <v>3.865</v>
+        <v>4.615</v>
       </c>
     </row>
     <row r="35">
@@ -20470,55 +20638,55 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>3.469</v>
+        <v>2.812</v>
       </c>
       <c r="F35" t="n">
-        <v>3.583</v>
+        <v>3.094</v>
       </c>
       <c r="G35" t="n">
-        <v>4.021</v>
+        <v>3.24</v>
       </c>
       <c r="H35" t="n">
-        <v>4.146</v>
+        <v>3.448</v>
       </c>
       <c r="I35" t="n">
-        <v>0.444</v>
+        <v>0.476</v>
       </c>
       <c r="J35" t="n">
-        <v>0.137</v>
+        <v>0.175</v>
       </c>
       <c r="K35" t="n">
         <v>0.078</v>
       </c>
       <c r="L35" t="n">
-        <v>0.032</v>
+        <v>0.029</v>
       </c>
       <c r="M35" t="n">
-        <v>0.144</v>
+        <v>0.091</v>
       </c>
       <c r="N35" t="n">
-        <v>0.186</v>
+        <v>0.133</v>
       </c>
       <c r="O35" t="n">
         <v>0.049</v>
       </c>
       <c r="P35" t="n">
-        <v>0.589</v>
+        <v>0.728</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.317</v>
+        <v>0.294</v>
       </c>
       <c r="R35" t="n">
-        <v>0.62</v>
+        <v>0.753</v>
       </c>
       <c r="S35" t="n">
-        <v>3.526</v>
+        <v>2.953</v>
       </c>
       <c r="T35" t="n">
-        <v>4.083</v>
+        <v>3.344</v>
       </c>
     </row>
     <row r="36">
@@ -20536,55 +20704,55 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>3.583</v>
+        <v>2.844</v>
       </c>
       <c r="F36" t="n">
-        <v>3.646</v>
+        <v>3.177</v>
       </c>
       <c r="G36" t="n">
-        <v>4.198</v>
+        <v>3.312</v>
       </c>
       <c r="H36" t="n">
-        <v>4.292</v>
+        <v>3.51</v>
       </c>
       <c r="I36" t="n">
-        <v>0.437</v>
+        <v>0.486</v>
       </c>
       <c r="J36" t="n">
-        <v>0.145</v>
+        <v>0.179</v>
       </c>
       <c r="K36" t="n">
-        <v>0.079</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>0.038</v>
+        <v>0.023</v>
       </c>
       <c r="M36" t="n">
-        <v>0.154</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>0.2</v>
+        <v>0.134</v>
       </c>
       <c r="O36" t="n">
-        <v>0.034</v>
+        <v>0.04</v>
       </c>
       <c r="P36" t="n">
-        <v>0.629</v>
+        <v>0.626</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.298</v>
+        <v>0.306</v>
       </c>
       <c r="R36" t="n">
-        <v>0.602</v>
+        <v>0.755</v>
       </c>
       <c r="S36" t="n">
-        <v>3.615</v>
+        <v>3.01</v>
       </c>
       <c r="T36" t="n">
-        <v>4.245</v>
+        <v>3.411</v>
       </c>
     </row>
     <row r="37">
@@ -20602,55 +20770,55 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>3.521</v>
+        <v>3.042</v>
       </c>
       <c r="F37" t="n">
-        <v>3.615</v>
+        <v>3.219</v>
       </c>
       <c r="G37" t="n">
-        <v>4.167</v>
+        <v>3.573</v>
       </c>
       <c r="H37" t="n">
-        <v>4.219</v>
+        <v>3.74</v>
       </c>
       <c r="I37" t="n">
-        <v>0.416</v>
+        <v>0.423</v>
       </c>
       <c r="J37" t="n">
-        <v>0.161</v>
+        <v>0.184</v>
       </c>
       <c r="K37" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.097</v>
       </c>
       <c r="L37" t="n">
-        <v>0.044</v>
+        <v>0.031</v>
       </c>
       <c r="M37" t="n">
-        <v>0.166</v>
+        <v>0.118</v>
       </c>
       <c r="N37" t="n">
-        <v>0.19</v>
+        <v>0.152</v>
       </c>
       <c r="O37" t="n">
-        <v>0.042</v>
+        <v>0.03</v>
       </c>
       <c r="P37" t="n">
-        <v>0.663</v>
+        <v>0.764</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.297</v>
+        <v>0.342</v>
       </c>
       <c r="R37" t="n">
-        <v>0.608</v>
+        <v>0.72</v>
       </c>
       <c r="S37" t="n">
-        <v>3.568</v>
+        <v>3.13</v>
       </c>
       <c r="T37" t="n">
-        <v>4.193</v>
+        <v>3.656</v>
       </c>
     </row>
     <row r="38">
@@ -20668,55 +20836,55 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>3.656</v>
+        <v>3.25</v>
       </c>
       <c r="F38" t="n">
-        <v>3.75</v>
+        <v>3.469</v>
       </c>
       <c r="G38" t="n">
-        <v>4.302</v>
+        <v>3.792</v>
       </c>
       <c r="H38" t="n">
-        <v>4.354</v>
+        <v>3.938</v>
       </c>
       <c r="I38" t="n">
-        <v>0.409</v>
+        <v>0.454</v>
       </c>
       <c r="J38" t="n">
-        <v>0.159</v>
+        <v>0.161</v>
       </c>
       <c r="K38" t="n">
-        <v>0.103</v>
+        <v>0.092</v>
       </c>
       <c r="L38" t="n">
-        <v>0.03</v>
+        <v>0.026</v>
       </c>
       <c r="M38" t="n">
-        <v>0.152</v>
+        <v>0.123</v>
       </c>
       <c r="N38" t="n">
-        <v>0.182</v>
+        <v>0.16</v>
       </c>
       <c r="O38" t="n">
-        <v>0.03</v>
+        <v>0.034</v>
       </c>
       <c r="P38" t="n">
-        <v>0.78</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.367</v>
+        <v>0.321</v>
       </c>
       <c r="R38" t="n">
-        <v>0.627</v>
+        <v>0.678</v>
       </c>
       <c r="S38" t="n">
-        <v>3.703</v>
+        <v>3.359</v>
       </c>
       <c r="T38" t="n">
-        <v>4.328</v>
+        <v>3.865</v>
       </c>
     </row>
     <row r="39">
@@ -20734,55 +20902,55 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
-        <v>3.771</v>
+        <v>3.469</v>
       </c>
       <c r="F39" t="n">
-        <v>3.729</v>
+        <v>3.583</v>
       </c>
       <c r="G39" t="n">
-        <v>4.49</v>
+        <v>4.021</v>
       </c>
       <c r="H39" t="n">
-        <v>4.448</v>
+        <v>4.146</v>
       </c>
       <c r="I39" t="n">
-        <v>0.393</v>
+        <v>0.444</v>
       </c>
       <c r="J39" t="n">
-        <v>0.159</v>
+        <v>0.137</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1</v>
+        <v>0.078</v>
       </c>
       <c r="L39" t="n">
-        <v>0.024</v>
+        <v>0.032</v>
       </c>
       <c r="M39" t="n">
-        <v>0.167</v>
+        <v>0.144</v>
       </c>
       <c r="N39" t="n">
         <v>0.186</v>
       </c>
       <c r="O39" t="n">
-        <v>0.019</v>
+        <v>0.049</v>
       </c>
       <c r="P39" t="n">
-        <v>0.726</v>
+        <v>0.589</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.364</v>
+        <v>0.317</v>
       </c>
       <c r="R39" t="n">
-        <v>0.609</v>
+        <v>0.62</v>
       </c>
       <c r="S39" t="n">
-        <v>3.75</v>
+        <v>3.526</v>
       </c>
       <c r="T39" t="n">
-        <v>4.469</v>
+        <v>4.083</v>
       </c>
     </row>
     <row r="40">
@@ -20800,55 +20968,55 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>3.76</v>
+        <v>3.583</v>
       </c>
       <c r="F40" t="n">
-        <v>3.812</v>
+        <v>3.646</v>
       </c>
       <c r="G40" t="n">
-        <v>4.5</v>
+        <v>4.198</v>
       </c>
       <c r="H40" t="n">
-        <v>4.542</v>
+        <v>4.292</v>
       </c>
       <c r="I40" t="n">
-        <v>0.384</v>
+        <v>0.437</v>
       </c>
       <c r="J40" t="n">
-        <v>0.173</v>
+        <v>0.145</v>
       </c>
       <c r="K40" t="n">
-        <v>0.108</v>
+        <v>0.079</v>
       </c>
       <c r="L40" t="n">
-        <v>0.047</v>
+        <v>0.038</v>
       </c>
       <c r="M40" t="n">
-        <v>0.157</v>
+        <v>0.154</v>
       </c>
       <c r="N40" t="n">
-        <v>0.175</v>
+        <v>0.2</v>
       </c>
       <c r="O40" t="n">
-        <v>0.039</v>
+        <v>0.034</v>
       </c>
       <c r="P40" t="n">
-        <v>0.873</v>
+        <v>0.629</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.357</v>
+        <v>0.298</v>
       </c>
       <c r="R40" t="n">
-        <v>0.659</v>
+        <v>0.602</v>
       </c>
       <c r="S40" t="n">
-        <v>3.786</v>
+        <v>3.615</v>
       </c>
       <c r="T40" t="n">
-        <v>4.521</v>
+        <v>4.245</v>
       </c>
     </row>
     <row r="41">
@@ -20866,54 +21034,318 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
+        <v>3.521</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.615</v>
+      </c>
+      <c r="G41" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4.219</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.568</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4.193</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.656</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G42" t="n">
+        <v>4.302</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.354</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.703</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4.328</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.771</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.729</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4.448</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4.469</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3.812</v>
+      </c>
+      <c r="G44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4.542</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.173</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.157</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.786</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4.521</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="n">
         <v>3.938</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F45" t="n">
         <v>3.938</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G45" t="n">
         <v>4.583</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H45" t="n">
         <v>4.573</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I45" t="n">
         <v>0.376</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J45" t="n">
         <v>0.18</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K45" t="n">
         <v>0.116</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L45" t="n">
         <v>0.043</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M45" t="n">
         <v>0.156</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N45" t="n">
         <v>0.166</v>
       </c>
-      <c r="O41" t="n">
+      <c r="O45" t="n">
         <v>0.034</v>
       </c>
-      <c r="P41" t="n">
+      <c r="P45" t="n">
         <v>0.951</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q45" t="n">
         <v>0.369</v>
       </c>
-      <c r="R41" t="n">
+      <c r="R45" t="n">
         <v>0.664</v>
       </c>
-      <c r="S41" t="n">
+      <c r="S45" t="n">
         <v>3.938</v>
       </c>
-      <c r="T41" t="n">
+      <c r="T45" t="n">
         <v>4.578</v>
       </c>
     </row>
@@ -21491,13 +21923,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
         <v>2.833</v>
       </c>
       <c r="H18" t="n">
-        <v>1.073</v>
+        <v>1.479</v>
       </c>
     </row>
     <row r="19">
@@ -21522,13 +21954,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G19" t="n">
         <v>3.042</v>
       </c>
       <c r="H19" t="n">
-        <v>0.896</v>
+        <v>1.219</v>
       </c>
     </row>
     <row r="20">
@@ -21553,13 +21985,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G20" t="n">
         <v>3.146</v>
       </c>
       <c r="H20" t="n">
-        <v>1.406</v>
+        <v>1.646</v>
       </c>
     </row>
     <row r="21">
@@ -21584,13 +22016,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G21" t="n">
         <v>3.458</v>
       </c>
       <c r="H21" t="n">
-        <v>1.146</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="22">
@@ -21615,13 +22047,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G22" t="n">
         <v>0.471</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.099</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="23">
@@ -21646,13 +22078,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
         <v>0.199</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.02</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="24">
@@ -21677,13 +22109,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G24" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>0.011</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="25">
@@ -21708,13 +22140,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G25" t="n">
         <v>0.026</v>
       </c>
       <c r="H25" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="26">
@@ -21739,13 +22171,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
         <v>0.078</v>
       </c>
       <c r="H26" t="n">
-        <v>0.095</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="27">
@@ -21770,13 +22202,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G27" t="n">
         <v>0.119</v>
       </c>
       <c r="H27" t="n">
-        <v>0.06</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="28">
@@ -21801,13 +22233,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
         <v>0.038</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.013</v>
+        <v>-0.024</v>
       </c>
     </row>
     <row r="29">
@@ -21832,13 +22264,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G29" t="n">
         <v>0.765</v>
       </c>
       <c r="H29" t="n">
-        <v>0.025</v>
+        <v>0.349</v>
       </c>
     </row>
     <row r="30">
@@ -21863,13 +22295,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
         <v>0.276</v>
       </c>
       <c r="H30" t="n">
-        <v>0.048</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="31">
@@ -21894,13 +22326,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G31" t="n">
         <v>0.793</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.168</v>
+        <v>-0.08699999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -21925,13 +22357,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
         <v>2.938</v>
       </c>
       <c r="H32" t="n">
-        <v>0.984</v>
+        <v>1.349</v>
       </c>
     </row>
     <row r="33">
@@ -21956,13 +22388,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G33" t="n">
         <v>3.302</v>
       </c>
       <c r="H33" t="n">
-        <v>1.276</v>
+        <v>1.484</v>
       </c>
     </row>
     <row r="34">
@@ -23475,13 +23907,13 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G82" t="n">
         <v>2.833</v>
       </c>
       <c r="H82" t="n">
-        <v>1.073</v>
+        <v>1.479</v>
       </c>
     </row>
     <row r="83">
@@ -23506,13 +23938,13 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G83" t="n">
         <v>3.042</v>
       </c>
       <c r="H83" t="n">
-        <v>0.896</v>
+        <v>1.219</v>
       </c>
     </row>
     <row r="84">
@@ -23537,13 +23969,13 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G84" t="n">
         <v>3.146</v>
       </c>
       <c r="H84" t="n">
-        <v>1.406</v>
+        <v>1.646</v>
       </c>
     </row>
     <row r="85">
@@ -23568,13 +24000,13 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G85" t="n">
         <v>3.458</v>
       </c>
       <c r="H85" t="n">
-        <v>1.146</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="86">
@@ -23599,13 +24031,13 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G86" t="n">
         <v>0.471</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.099</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="87">
@@ -23630,13 +24062,13 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G87" t="n">
         <v>0.199</v>
       </c>
       <c r="H87" t="n">
-        <v>-0.02</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="88">
@@ -23661,13 +24093,13 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G88" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>0.011</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="89">
@@ -23692,13 +24124,13 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G89" t="n">
         <v>0.026</v>
       </c>
       <c r="H89" t="n">
-        <v>0.008</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="90">
@@ -23723,13 +24155,13 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G90" t="n">
         <v>0.078</v>
       </c>
       <c r="H90" t="n">
-        <v>0.095</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="91">
@@ -23754,13 +24186,13 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G91" t="n">
         <v>0.119</v>
       </c>
       <c r="H91" t="n">
-        <v>0.06</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="92">
@@ -23785,13 +24217,13 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G92" t="n">
         <v>0.038</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.013</v>
+        <v>-0.024</v>
       </c>
     </row>
     <row r="93">
@@ -23816,13 +24248,13 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G93" t="n">
         <v>0.765</v>
       </c>
       <c r="H93" t="n">
-        <v>0.025</v>
+        <v>0.349</v>
       </c>
     </row>
     <row r="94">
@@ -23847,13 +24279,13 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G94" t="n">
         <v>0.276</v>
       </c>
       <c r="H94" t="n">
-        <v>0.048</v>
+        <v>0.134</v>
       </c>
     </row>
     <row r="95">
@@ -23878,13 +24310,13 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G95" t="n">
         <v>0.793</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.168</v>
+        <v>-0.08699999999999999</v>
       </c>
     </row>
     <row r="96">
@@ -23909,13 +24341,13 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G96" t="n">
         <v>2.938</v>
       </c>
       <c r="H96" t="n">
-        <v>0.984</v>
+        <v>1.349</v>
       </c>
     </row>
     <row r="97">
@@ -23940,13 +24372,13 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G97" t="n">
         <v>3.302</v>
       </c>
       <c r="H97" t="n">
-        <v>1.276</v>
+        <v>1.484</v>
       </c>
     </row>
     <row r="98">
@@ -25091,27 +25523,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>final (iter 6)</t>
+          <t>final (iter 10)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.79 ✗</t>
+          <t>1.11 ✓fair</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32 ✗</t>
+          <t>0.41 ✓fair</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.92 ✓fair</t>
+          <t>4.29 ✓good</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4.58 ✓good</t>
+          <t>4.79 ✓good</t>
         </is>
       </c>
     </row>
@@ -25254,7 +25686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26078,169 +26510,169 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>3.427</v>
+        <v>3.875</v>
       </c>
       <c r="F20" t="n">
-        <v>2.719</v>
+        <v>3.281</v>
       </c>
       <c r="G20" t="n">
-        <v>3.083</v>
+        <v>3.927</v>
       </c>
       <c r="H20" t="n">
-        <v>3.076</v>
+        <v>3.694</v>
       </c>
       <c r="I20" t="n">
-        <v>0.489</v>
+        <v>0.621</v>
       </c>
       <c r="J20" t="n">
-        <v>0.419</v>
+        <v>0.545</v>
       </c>
       <c r="K20" t="n">
-        <v>0.43</v>
+        <v>0.327</v>
       </c>
       <c r="L20" t="n">
-        <v>0.151</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>3.396</v>
+        <v>3.917</v>
       </c>
       <c r="F21" t="n">
-        <v>2.75</v>
+        <v>3.188</v>
       </c>
       <c r="G21" t="n">
-        <v>3.073</v>
+        <v>3.865</v>
       </c>
       <c r="H21" t="n">
-        <v>3.073</v>
+        <v>3.656</v>
       </c>
       <c r="I21" t="n">
-        <v>0.459</v>
+        <v>0.627</v>
       </c>
       <c r="J21" t="n">
-        <v>0.39</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.459</v>
+        <v>0.319</v>
       </c>
       <c r="L21" t="n">
-        <v>0.152</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>3.458</v>
+        <v>4.177</v>
       </c>
       <c r="F22" t="n">
-        <v>2.854</v>
+        <v>3.417</v>
       </c>
       <c r="G22" t="n">
-        <v>3.229</v>
+        <v>4.198</v>
       </c>
       <c r="H22" t="n">
-        <v>3.181</v>
+        <v>3.931</v>
       </c>
       <c r="I22" t="n">
-        <v>0.491</v>
+        <v>0.699</v>
       </c>
       <c r="J22" t="n">
-        <v>0.416</v>
+        <v>0.626</v>
       </c>
       <c r="K22" t="n">
-        <v>0.428</v>
+        <v>0.265</v>
       </c>
       <c r="L22" t="n">
-        <v>0.156</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PTO_LA0</t>
+          <t>GRPO_LA5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GRPO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>3.479</v>
+        <v>4.094</v>
       </c>
       <c r="F23" t="n">
-        <v>2.906</v>
+        <v>3.396</v>
       </c>
       <c r="G23" t="n">
-        <v>3.406</v>
+        <v>4.104</v>
       </c>
       <c r="H23" t="n">
-        <v>3.264</v>
+        <v>3.865</v>
       </c>
       <c r="I23" t="n">
-        <v>0.533</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>0.469</v>
+        <v>0.617</v>
       </c>
       <c r="K23" t="n">
-        <v>0.403</v>
+        <v>0.276</v>
       </c>
       <c r="L23" t="n">
-        <v>0.127</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="24">
@@ -26258,31 +26690,31 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>3.594</v>
+        <v>3.427</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2.719</v>
       </c>
       <c r="G24" t="n">
-        <v>3.51</v>
+        <v>3.083</v>
       </c>
       <c r="H24" t="n">
-        <v>3.368</v>
+        <v>3.076</v>
       </c>
       <c r="I24" t="n">
-        <v>0.538</v>
+        <v>0.489</v>
       </c>
       <c r="J24" t="n">
-        <v>0.465</v>
+        <v>0.419</v>
       </c>
       <c r="K24" t="n">
-        <v>0.404</v>
+        <v>0.43</v>
       </c>
       <c r="L24" t="n">
-        <v>0.131</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="25">
@@ -26300,31 +26732,31 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>3.542</v>
+        <v>3.396</v>
       </c>
       <c r="F25" t="n">
-        <v>2.969</v>
+        <v>2.75</v>
       </c>
       <c r="G25" t="n">
-        <v>3.51</v>
+        <v>3.073</v>
       </c>
       <c r="H25" t="n">
-        <v>3.34</v>
+        <v>3.073</v>
       </c>
       <c r="I25" t="n">
-        <v>0.555</v>
+        <v>0.459</v>
       </c>
       <c r="J25" t="n">
-        <v>0.478</v>
+        <v>0.39</v>
       </c>
       <c r="K25" t="n">
-        <v>0.387</v>
+        <v>0.459</v>
       </c>
       <c r="L25" t="n">
-        <v>0.135</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="26">
@@ -26342,31 +26774,31 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>3.688</v>
+        <v>3.458</v>
       </c>
       <c r="F26" t="n">
-        <v>3.052</v>
+        <v>2.854</v>
       </c>
       <c r="G26" t="n">
-        <v>3.667</v>
+        <v>3.229</v>
       </c>
       <c r="H26" t="n">
-        <v>3.469</v>
+        <v>3.181</v>
       </c>
       <c r="I26" t="n">
-        <v>0.569</v>
+        <v>0.491</v>
       </c>
       <c r="J26" t="n">
-        <v>0.507</v>
+        <v>0.416</v>
       </c>
       <c r="K26" t="n">
-        <v>0.376</v>
+        <v>0.428</v>
       </c>
       <c r="L26" t="n">
-        <v>0.117</v>
+        <v>0.156</v>
       </c>
     </row>
     <row r="27">
@@ -26384,31 +26816,31 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>3.562</v>
+        <v>3.479</v>
       </c>
       <c r="F27" t="n">
-        <v>2.969</v>
+        <v>2.906</v>
       </c>
       <c r="G27" t="n">
-        <v>3.531</v>
+        <v>3.406</v>
       </c>
       <c r="H27" t="n">
-        <v>3.354</v>
+        <v>3.264</v>
       </c>
       <c r="I27" t="n">
-        <v>0.545</v>
+        <v>0.533</v>
       </c>
       <c r="J27" t="n">
-        <v>0.477</v>
+        <v>0.469</v>
       </c>
       <c r="K27" t="n">
-        <v>0.399</v>
+        <v>0.403</v>
       </c>
       <c r="L27" t="n">
-        <v>0.124</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="28">
@@ -26426,31 +26858,31 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>3.688</v>
+        <v>3.594</v>
       </c>
       <c r="F28" t="n">
-        <v>3.073</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>3.688</v>
+        <v>3.51</v>
       </c>
       <c r="H28" t="n">
-        <v>3.483</v>
+        <v>3.368</v>
       </c>
       <c r="I28" t="n">
-        <v>0.573</v>
+        <v>0.538</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5</v>
+        <v>0.465</v>
       </c>
       <c r="K28" t="n">
-        <v>0.379</v>
+        <v>0.404</v>
       </c>
       <c r="L28" t="n">
-        <v>0.121</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="29">
@@ -26468,31 +26900,31 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>3.76</v>
+        <v>3.542</v>
       </c>
       <c r="F29" t="n">
-        <v>3.156</v>
+        <v>2.969</v>
       </c>
       <c r="G29" t="n">
-        <v>3.833</v>
+        <v>3.51</v>
       </c>
       <c r="H29" t="n">
-        <v>3.583</v>
+        <v>3.34</v>
       </c>
       <c r="I29" t="n">
-        <v>0.612</v>
+        <v>0.555</v>
       </c>
       <c r="J29" t="n">
-        <v>0.545</v>
+        <v>0.478</v>
       </c>
       <c r="K29" t="n">
-        <v>0.335</v>
+        <v>0.387</v>
       </c>
       <c r="L29" t="n">
-        <v>0.12</v>
+        <v>0.135</v>
       </c>
     </row>
     <row r="30">
@@ -26510,37 +26942,37 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>3.802</v>
+        <v>3.688</v>
       </c>
       <c r="F30" t="n">
-        <v>3.177</v>
+        <v>3.052</v>
       </c>
       <c r="G30" t="n">
-        <v>3.833</v>
+        <v>3.667</v>
       </c>
       <c r="H30" t="n">
-        <v>3.604</v>
+        <v>3.469</v>
       </c>
       <c r="I30" t="n">
-        <v>0.63</v>
+        <v>0.569</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.507</v>
       </c>
       <c r="K30" t="n">
-        <v>0.327</v>
+        <v>0.376</v>
       </c>
       <c r="L30" t="n">
-        <v>0.113</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -26549,40 +26981,40 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E31" t="n">
+        <v>3.562</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.969</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3.531</v>
+      </c>
+      <c r="H31" t="n">
         <v>3.354</v>
       </c>
-      <c r="F31" t="n">
-        <v>2.708</v>
-      </c>
-      <c r="G31" t="n">
-        <v>3.146</v>
-      </c>
-      <c r="H31" t="n">
-        <v>3.069</v>
-      </c>
       <c r="I31" t="n">
-        <v>0.481</v>
+        <v>0.545</v>
       </c>
       <c r="J31" t="n">
-        <v>0.406</v>
+        <v>0.477</v>
       </c>
       <c r="K31" t="n">
-        <v>0.442</v>
+        <v>0.399</v>
       </c>
       <c r="L31" t="n">
-        <v>0.152</v>
+        <v>0.124</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -26591,40 +27023,40 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>3.406</v>
+        <v>3.688</v>
       </c>
       <c r="F32" t="n">
-        <v>2.792</v>
+        <v>3.073</v>
       </c>
       <c r="G32" t="n">
-        <v>3.031</v>
+        <v>3.688</v>
       </c>
       <c r="H32" t="n">
-        <v>3.076</v>
+        <v>3.483</v>
       </c>
       <c r="I32" t="n">
-        <v>0.487</v>
+        <v>0.573</v>
       </c>
       <c r="J32" t="n">
-        <v>0.412</v>
+        <v>0.5</v>
       </c>
       <c r="K32" t="n">
-        <v>0.441</v>
+        <v>0.379</v>
       </c>
       <c r="L32" t="n">
-        <v>0.147</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -26633,40 +27065,40 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E33" t="n">
-        <v>3.448</v>
+        <v>3.76</v>
       </c>
       <c r="F33" t="n">
-        <v>2.812</v>
+        <v>3.156</v>
       </c>
       <c r="G33" t="n">
-        <v>3.26</v>
+        <v>3.833</v>
       </c>
       <c r="H33" t="n">
-        <v>3.174</v>
+        <v>3.583</v>
       </c>
       <c r="I33" t="n">
-        <v>0.495</v>
+        <v>0.612</v>
       </c>
       <c r="J33" t="n">
-        <v>0.425</v>
+        <v>0.545</v>
       </c>
       <c r="K33" t="n">
-        <v>0.43</v>
+        <v>0.335</v>
       </c>
       <c r="L33" t="n">
-        <v>0.145</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PTO_LA5</t>
+          <t>PTO_LA0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -26675,34 +27107,34 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>3.646</v>
+        <v>3.802</v>
       </c>
       <c r="F34" t="n">
-        <v>2.969</v>
+        <v>3.177</v>
       </c>
       <c r="G34" t="n">
-        <v>3.479</v>
+        <v>3.833</v>
       </c>
       <c r="H34" t="n">
-        <v>3.365</v>
+        <v>3.604</v>
       </c>
       <c r="I34" t="n">
-        <v>0.531</v>
+        <v>0.63</v>
       </c>
       <c r="J34" t="n">
-        <v>0.454</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>0.394</v>
+        <v>0.327</v>
       </c>
       <c r="L34" t="n">
-        <v>0.152</v>
+        <v>0.113</v>
       </c>
     </row>
     <row r="35">
@@ -26720,31 +27152,31 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>3.719</v>
+        <v>3.354</v>
       </c>
       <c r="F35" t="n">
-        <v>3.021</v>
+        <v>2.708</v>
       </c>
       <c r="G35" t="n">
-        <v>3.635</v>
+        <v>3.146</v>
       </c>
       <c r="H35" t="n">
-        <v>3.458</v>
+        <v>3.069</v>
       </c>
       <c r="I35" t="n">
-        <v>0.556</v>
+        <v>0.481</v>
       </c>
       <c r="J35" t="n">
-        <v>0.488</v>
+        <v>0.406</v>
       </c>
       <c r="K35" t="n">
-        <v>0.385</v>
+        <v>0.442</v>
       </c>
       <c r="L35" t="n">
-        <v>0.127</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="36">
@@ -26762,31 +27194,31 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
-        <v>3.729</v>
+        <v>3.406</v>
       </c>
       <c r="F36" t="n">
-        <v>3.042</v>
+        <v>2.792</v>
       </c>
       <c r="G36" t="n">
-        <v>3.667</v>
+        <v>3.031</v>
       </c>
       <c r="H36" t="n">
-        <v>3.479</v>
+        <v>3.076</v>
       </c>
       <c r="I36" t="n">
-        <v>0.575</v>
+        <v>0.487</v>
       </c>
       <c r="J36" t="n">
-        <v>0.506</v>
+        <v>0.412</v>
       </c>
       <c r="K36" t="n">
-        <v>0.377</v>
+        <v>0.441</v>
       </c>
       <c r="L36" t="n">
-        <v>0.116</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="37">
@@ -26804,31 +27236,31 @@
         <v>5</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
-        <v>3.688</v>
+        <v>3.448</v>
       </c>
       <c r="F37" t="n">
-        <v>3.062</v>
+        <v>2.812</v>
       </c>
       <c r="G37" t="n">
-        <v>3.625</v>
+        <v>3.26</v>
       </c>
       <c r="H37" t="n">
-        <v>3.458</v>
+        <v>3.174</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.495</v>
       </c>
       <c r="J37" t="n">
-        <v>0.493</v>
+        <v>0.425</v>
       </c>
       <c r="K37" t="n">
-        <v>0.374</v>
+        <v>0.43</v>
       </c>
       <c r="L37" t="n">
-        <v>0.133</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="38">
@@ -26846,31 +27278,31 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>3.75</v>
+        <v>3.646</v>
       </c>
       <c r="F38" t="n">
-        <v>3.115</v>
+        <v>2.969</v>
       </c>
       <c r="G38" t="n">
-        <v>3.729</v>
+        <v>3.479</v>
       </c>
       <c r="H38" t="n">
-        <v>3.531</v>
+        <v>3.365</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.531</v>
       </c>
       <c r="J38" t="n">
-        <v>0.499</v>
+        <v>0.454</v>
       </c>
       <c r="K38" t="n">
-        <v>0.375</v>
+        <v>0.394</v>
       </c>
       <c r="L38" t="n">
-        <v>0.125</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="39">
@@ -26888,31 +27320,31 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
         <v>3.719</v>
       </c>
       <c r="F39" t="n">
-        <v>3.156</v>
+        <v>3.021</v>
       </c>
       <c r="G39" t="n">
-        <v>3.812</v>
+        <v>3.635</v>
       </c>
       <c r="H39" t="n">
-        <v>3.562</v>
+        <v>3.458</v>
       </c>
       <c r="I39" t="n">
-        <v>0.587</v>
+        <v>0.556</v>
       </c>
       <c r="J39" t="n">
-        <v>0.512</v>
+        <v>0.488</v>
       </c>
       <c r="K39" t="n">
-        <v>0.356</v>
+        <v>0.385</v>
       </c>
       <c r="L39" t="n">
-        <v>0.132</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="40">
@@ -26930,31 +27362,31 @@
         <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E40" t="n">
-        <v>3.844</v>
+        <v>3.729</v>
       </c>
       <c r="F40" t="n">
-        <v>3.146</v>
+        <v>3.042</v>
       </c>
       <c r="G40" t="n">
-        <v>3.76</v>
+        <v>3.667</v>
       </c>
       <c r="H40" t="n">
-        <v>3.583</v>
+        <v>3.479</v>
       </c>
       <c r="I40" t="n">
-        <v>0.594</v>
+        <v>0.575</v>
       </c>
       <c r="J40" t="n">
-        <v>0.523</v>
+        <v>0.506</v>
       </c>
       <c r="K40" t="n">
-        <v>0.347</v>
+        <v>0.377</v>
       </c>
       <c r="L40" t="n">
-        <v>0.131</v>
+        <v>0.116</v>
       </c>
     </row>
     <row r="41">
@@ -26972,30 +27404,198 @@
         <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E41" t="n">
+        <v>3.688</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3.062</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3.458</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.133</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="F42" t="n">
+        <v>3.115</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3.729</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3.531</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>5</v>
+      </c>
+      <c r="D43" t="n">
+        <v>8</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.719</v>
+      </c>
+      <c r="F43" t="n">
+        <v>3.156</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3.812</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.562</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.132</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3.844</v>
+      </c>
+      <c r="F44" t="n">
+        <v>3.146</v>
+      </c>
+      <c r="G44" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="H44" t="n">
+        <v>3.583</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.131</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PTO_LA5</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="n">
         <v>3.958</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F45" t="n">
         <v>3.229</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G45" t="n">
         <v>3.958</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H45" t="n">
         <v>3.715</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I45" t="n">
         <v>0.638</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J45" t="n">
         <v>0.5679999999999999</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K45" t="n">
         <v>0.315</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L45" t="n">
         <v>0.117</v>
       </c>
     </row>
